--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$P$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$P$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -68,7 +69,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -548,7 +549,6 @@
         <v>45762</v>
       </c>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>India</t>
@@ -569,8 +569,6 @@
           <t>Salesforce</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -594,7 +592,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,7 +605,6 @@
       <c r="C3" s="2" t="n">
         <v>46031</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Other</t>
@@ -624,9 +620,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -650,7 +643,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -664,7 +656,6 @@
       <c r="C4" s="2" t="n">
         <v>46031</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Other</t>
@@ -680,9 +671,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -706,7 +694,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -720,7 +707,6 @@
       <c r="C5" s="2" t="n">
         <v>46035</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>New York</t>
@@ -736,10 +722,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>https://nrfbigshow.nrf.com/</t>
@@ -758,7 +740,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -770,7 +751,6 @@
         <v>46035</v>
       </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Other</t>
@@ -791,8 +771,6 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -816,7 +794,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -828,7 +805,6 @@
         <v>46037</v>
       </c>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -849,8 +825,6 @@
           <t>MongoDB</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>50</t>
@@ -874,7 +848,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -886,7 +859,6 @@
         <v>46037</v>
       </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Other</t>
@@ -907,8 +879,6 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -932,7 +902,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -944,13 +913,11 @@
         <v>46042</v>
       </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>In-person</t>
@@ -961,9 +928,6 @@
           <t>AWS, Snowflake</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>https://www.snowflake.com/event/snowflake-on-aws-launch-event-20-january/</t>
@@ -982,7 +946,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -994,7 +957,6 @@
         <v>46043</v>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>New York</t>
@@ -1015,8 +977,6 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1040,7 +1000,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1052,7 +1011,6 @@
         <v>46044</v>
       </c>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>India</t>
@@ -1073,8 +1031,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1098,7 +1054,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1112,7 +1067,6 @@
       <c r="C12" s="2" t="n">
         <v>46050</v>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -1133,8 +1087,6 @@
           <t>Acumatica</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1158,7 +1110,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1172,7 +1123,6 @@
       <c r="C13" s="2" t="n">
         <v>46051</v>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1193,8 +1143,6 @@
           <t>Dynatrace</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>1495</t>
@@ -1218,7 +1166,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1230,7 +1177,6 @@
         <v>46049</v>
       </c>
       <c r="C14" s="2" t="n"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1251,8 +1197,6 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1276,7 +1220,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1288,7 +1231,6 @@
         <v>46063</v>
       </c>
       <c r="C15" s="2" t="n"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>India</t>
@@ -1309,8 +1251,6 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1334,7 +1274,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1348,7 +1287,6 @@
       <c r="C16" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>India</t>
@@ -1364,10 +1302,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
           <t>https://kripeshadwani.com/best-tech-events-in-india/#ai-impact-summit-2026</t>
@@ -1386,7 +1320,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1398,7 +1331,6 @@
         <v>46070</v>
       </c>
       <c r="C17" s="2" t="n"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>India</t>
@@ -1419,8 +1351,6 @@
           <t>NetApp</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1444,7 +1374,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1456,7 +1385,6 @@
         <v>46071</v>
       </c>
       <c r="C18" s="2" t="n"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>India</t>
@@ -1472,9 +1400,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1498,7 +1423,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1510,7 +1434,6 @@
         <v>46080</v>
       </c>
       <c r="C19" s="2" t="n"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>India</t>
@@ -1531,8 +1454,6 @@
           <t>Commvault</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1556,7 +1477,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1570,7 +1490,6 @@
       <c r="C20" s="2" t="n">
         <v>46084</v>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1586,9 +1505,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1612,7 +1528,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1626,7 +1541,6 @@
       <c r="C21" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1647,8 +1561,6 @@
           <t>Fortinet</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1672,7 +1584,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1684,7 +1595,6 @@
         <v>46091</v>
       </c>
       <c r="C22" s="2" t="n"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1705,8 +1615,6 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1730,7 +1638,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1744,7 +1651,6 @@
       <c r="C23" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -1765,8 +1671,6 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1790,7 +1694,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1804,7 +1707,6 @@
       <c r="C24" s="2" t="n">
         <v>46099</v>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1820,9 +1722,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1846,7 +1745,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1860,7 +1758,6 @@
       <c r="C25" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1881,8 +1778,6 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -1906,7 +1801,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1920,7 +1814,6 @@
       <c r="C26" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -1941,8 +1834,6 @@
           <t>Qualtrics</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>1299</t>
@@ -1966,7 +1857,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1980,7 +1870,6 @@
       <c r="C27" s="2" t="n">
         <v>46121</v>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -1996,9 +1885,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>2650</t>
@@ -2022,7 +1908,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2036,7 +1921,6 @@
       <c r="C28" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2052,9 +1936,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>1200</t>
@@ -2078,7 +1959,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2092,7 +1972,6 @@
       <c r="C29" s="2" t="n">
         <v>46121</v>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2113,8 +1992,6 @@
           <t>Nutanix</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -2138,7 +2015,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2152,7 +2028,6 @@
       <c r="C30" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Texas</t>
@@ -2173,8 +2048,6 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>875</t>
@@ -2198,7 +2071,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2210,13 +2082,11 @@
         <v>46126</v>
       </c>
       <c r="C31" s="2" t="n"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>In-person</t>
@@ -2227,8 +2097,6 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -2252,7 +2120,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2266,7 +2133,6 @@
       <c r="C32" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2287,8 +2153,6 @@
           <t>Adobe</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -2312,7 +2176,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2326,7 +2189,6 @@
       <c r="C33" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2347,8 +2209,6 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>999</t>
@@ -2372,7 +2232,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2384,7 +2243,6 @@
         <v>46135</v>
       </c>
       <c r="C34" s="2" t="n"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2400,9 +2258,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -2426,7 +2281,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2440,7 +2294,6 @@
       <c r="C35" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -2456,9 +2309,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>499-1599</t>
@@ -2482,7 +2332,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2496,7 +2345,6 @@
       <c r="C36" s="2" t="n">
         <v>46149</v>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2517,8 +2365,6 @@
           <t>IBM</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -2542,7 +2388,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2556,7 +2401,6 @@
       <c r="C37" s="2" t="n">
         <v>46149</v>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2577,8 +2421,6 @@
           <t>ServiceNow</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>1795</t>
@@ -2602,7 +2444,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2616,7 +2457,6 @@
       <c r="C38" s="2" t="n">
         <v>46149</v>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2637,8 +2477,6 @@
           <t>Atlassian</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>699</t>
@@ -2662,7 +2500,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2676,7 +2513,6 @@
       <c r="C39" s="2" t="n">
         <v>46155</v>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2697,8 +2533,6 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -2722,7 +2556,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2736,7 +2569,6 @@
       <c r="C40" s="2" t="n">
         <v>46156</v>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -2752,9 +2584,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -2778,7 +2607,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2792,21 +2620,16 @@
       <c r="C41" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>In-person</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>1200-2500</t>
@@ -2830,7 +2653,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2844,7 +2666,6 @@
       <c r="C42" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2865,8 +2686,6 @@
           <t>Dell</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>1000</t>
@@ -2890,7 +2709,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2904,7 +2722,6 @@
       <c r="C43" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2925,8 +2742,6 @@
           <t>Zendesk</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -2950,7 +2765,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2964,13 +2778,11 @@
       <c r="C44" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>In-person</t>
@@ -2981,8 +2793,6 @@
           <t>Informatica</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -3006,7 +2816,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3018,7 +2827,6 @@
         <v>46161</v>
       </c>
       <c r="C45" s="2" t="n"/>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>India</t>
@@ -3039,8 +2847,6 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -3064,7 +2870,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3078,7 +2883,6 @@
       <c r="C46" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>New York</t>
@@ -3099,8 +2903,6 @@
           <t>Docusign</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -3124,7 +2926,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3136,7 +2937,6 @@
         <v>46173</v>
       </c>
       <c r="C47" s="2" t="n"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Other</t>
@@ -3157,8 +2957,6 @@
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>2795</t>
@@ -3182,7 +2980,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3196,7 +2993,6 @@
       <c r="C48" s="2" t="n">
         <v>46177</v>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -3217,9 +3013,6 @@
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" s="3" t="inlineStr">
         <is>
           <t>https://www.snowflake.com/en/summit/</t>
@@ -3238,7 +3031,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3252,7 +3044,6 @@
       <c r="C49" s="2" t="n">
         <v>46183</v>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>New York</t>
@@ -3273,8 +3064,6 @@
           <t>Datadog</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -3298,7 +3087,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3312,7 +3100,6 @@
       <c r="C50" s="2" t="n">
         <v>46191</v>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -3333,9 +3120,6 @@
           <t>Databricks</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" s="3" t="inlineStr">
         <is>
           <t>https://www.databricks.com/dataaisummit</t>
@@ -3354,7 +3138,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3368,7 +3151,6 @@
       <c r="C51" s="2" t="n">
         <v>46191</v>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Other</t>
@@ -3389,8 +3171,6 @@
           <t>Pure Storage</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -3414,7 +3194,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3428,7 +3207,6 @@
       <c r="C52" s="2" t="n">
         <v>46191</v>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3444,9 +3222,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>999</t>
@@ -3470,7 +3245,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3484,7 +3258,6 @@
       <c r="C53" s="2" t="n">
         <v>46191</v>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3500,9 +3273,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>999</t>
@@ -3526,7 +3296,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3540,7 +3309,6 @@
       <c r="C54" s="2" t="n">
         <v>46241</v>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3561,14 +3329,11 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>Not publicly listed</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -3582,7 +3347,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3596,7 +3360,6 @@
       <c r="C55" s="2" t="n">
         <v>46240</v>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Other</t>
@@ -3612,9 +3375,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>1395</t>
@@ -3638,7 +3398,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3650,7 +3409,6 @@
         <v>46245</v>
       </c>
       <c r="C56" s="2" t="n"/>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3671,14 +3429,11 @@
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>Not publicly listed</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -3692,7 +3447,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3704,7 +3458,6 @@
         <v>46245</v>
       </c>
       <c r="C57" s="2" t="n"/>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3725,8 +3478,6 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>Not publicly listed; application-based</t>
@@ -3750,7 +3501,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3762,7 +3512,6 @@
         <v>46245</v>
       </c>
       <c r="C58" s="2" t="n"/>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3778,9 +3527,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3804,7 +3550,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3816,7 +3561,6 @@
         <v>46245</v>
       </c>
       <c r="C59" s="2" t="n"/>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3837,14 +3581,11 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>Not publicly listed; currently waitlist</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -3858,7 +3599,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3870,7 +3610,6 @@
         <v>46245</v>
       </c>
       <c r="C60" s="2" t="n"/>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3886,9 +3625,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>$20 advance / $27 day-of</t>
@@ -3912,7 +3648,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3924,7 +3659,6 @@
         <v>46246</v>
       </c>
       <c r="C61" s="2" t="n"/>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3945,14 +3679,11 @@
           <t>AWS, Salesforce</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>Not publicly listed</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -3966,7 +3697,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3978,7 +3708,6 @@
         <v>46248</v>
       </c>
       <c r="C62" s="2" t="n"/>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3999,14 +3728,11 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>No public fee listed; approval required</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4020,7 +3746,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4034,7 +3759,6 @@
       <c r="C63" s="2" t="n">
         <v>46254</v>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4050,15 +3774,11 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>Not publicly listed</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4072,7 +3792,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4086,7 +3805,6 @@
       <c r="C64" s="2" t="n">
         <v>46254</v>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4102,15 +3820,11 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>Not publicly listed; accredited-investor access</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4124,7 +3838,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4136,7 +3849,6 @@
         <v>46254</v>
       </c>
       <c r="C65" s="2" t="n"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4157,14 +3869,11 @@
           <t>ServiceNow</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4178,7 +3887,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4190,7 +3898,6 @@
         <v>46255</v>
       </c>
       <c r="C66" s="2" t="n"/>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4211,14 +3918,11 @@
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4232,7 +3936,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4246,7 +3949,6 @@
       <c r="C67" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4267,8 +3969,6 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>1595-2695</t>
@@ -4292,7 +3992,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4306,7 +4005,6 @@
       <c r="C68" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4327,14 +4025,11 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>$1,825–$2,995 currently, depending on pass</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4348,7 +4043,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4360,7 +4054,6 @@
         <v>46265</v>
       </c>
       <c r="C69" s="2" t="n"/>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Other</t>
@@ -4371,15 +4064,11 @@
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>VMware</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" s="3" t="inlineStr">
         <is>
           <t>https://www.vmware.com/explore?view=all</t>
@@ -4398,7 +4087,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4412,7 +4100,6 @@
       <c r="C70" s="2" t="n">
         <v>46267</v>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4433,8 +4120,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>Invite only event</t>
@@ -4458,7 +4143,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4470,7 +4154,6 @@
         <v>46275</v>
       </c>
       <c r="C71" s="2" t="n"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4491,14 +4174,11 @@
           <t>Oracle, Intuit</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>Not publicly listed</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4512,7 +4192,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4524,7 +4203,6 @@
         <v>46275</v>
       </c>
       <c r="C72" s="2" t="n"/>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4545,14 +4223,11 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>No public fee listed; CISO/Sr. InfoSec qualification</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4566,7 +4241,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4578,7 +4252,6 @@
         <v>46275</v>
       </c>
       <c r="C73" s="2" t="n"/>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4594,15 +4267,11 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>From $299</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4616,7 +4285,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4628,7 +4296,6 @@
         <v>46275</v>
       </c>
       <c r="C74" s="2" t="n"/>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4644,15 +4311,11 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>Not publicly surfaced</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4666,7 +4329,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4678,7 +4340,6 @@
         <v>46275</v>
       </c>
       <c r="C75" s="2" t="n"/>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>New York</t>
@@ -4699,9 +4360,6 @@
           <t>ServiceNow</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" s="3" t="inlineStr">
         <is>
           <t>https://www.servicenow.com/events/world-forum.html</t>
@@ -4720,7 +4378,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4734,7 +4391,6 @@
       <c r="C76" s="2" t="n">
         <v>46282</v>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -4755,9 +4411,6 @@
           <t>Salesforce</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" s="3" t="inlineStr">
         <is>
           <t>https://www.salesforce.com/dreamforce/?d=pb</t>
@@ -4776,7 +4429,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4790,7 +4442,6 @@
       <c r="C77" s="2" t="n">
         <v>46289</v>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4811,14 +4462,11 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>Price not publicly surfaced; $100 early-bird discount through Aug 8</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4832,7 +4480,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4846,7 +4493,6 @@
       <c r="C78" s="2" t="n">
         <v>46289</v>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Other</t>
@@ -4867,9 +4513,6 @@
           <t>Okta</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" s="3" t="inlineStr">
         <is>
           <t>https://security.world/event/okta-oktane-2026/</t>
@@ -4888,7 +4531,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4902,7 +4544,6 @@
       <c r="C79" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4923,14 +4564,11 @@
           <t>Microsoft, AWS, Databricks</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>Invite-only / no public fee</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4944,7 +4582,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4956,7 +4593,6 @@
         <v>46295</v>
       </c>
       <c r="C80" s="2" t="n"/>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4977,14 +4613,11 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>Free / complimentary</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -4998,7 +4631,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5010,7 +4642,6 @@
         <v>46296</v>
       </c>
       <c r="C81" s="2" t="n"/>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -5031,14 +4662,11 @@
           <t>IBM</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>$250 standard admission</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -5052,7 +4680,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5066,7 +4693,6 @@
       <c r="C82" s="2" t="n">
         <v>46302</v>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Other</t>
@@ -5087,8 +4713,6 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -5112,7 +4736,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5126,7 +4749,6 @@
       <c r="C83" s="2" t="n">
         <v>46303</v>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>India</t>
@@ -5142,9 +4764,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>7000 (INR)</t>
@@ -5168,7 +4787,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5180,7 +4798,6 @@
         <v>46301</v>
       </c>
       <c r="C84" s="2" t="n"/>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>India</t>
@@ -5201,9 +4818,6 @@
           <t>ServiceNow</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr">
         <is>
           <t>https://www.servicenow.com/events/world-forum.html</t>
@@ -5222,7 +4836,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5236,7 +4849,6 @@
       <c r="C85" s="2" t="n">
         <v>46310</v>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Other</t>
@@ -5257,8 +4869,6 @@
           <t>Workday</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -5282,7 +4892,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5296,7 +4905,6 @@
       <c r="C86" s="2" t="n">
         <v>46310</v>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -5312,9 +4920,6 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -5338,7 +4943,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5350,7 +4954,6 @@
         <v>46309</v>
       </c>
       <c r="C87" s="2" t="n"/>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -5371,14 +4974,11 @@
           <t>Nutanix</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>Not publicly listed</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -5392,7 +4992,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5406,7 +5005,6 @@
       <c r="C88" s="2" t="n">
         <v>46317</v>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -5427,9 +5025,6 @@
           <t>Cloudflare</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" s="3" t="inlineStr">
         <is>
           <t>https://www.cloudflare.com/en-gb/lp/cloudflare-connect-2026/</t>
@@ -5448,7 +5043,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5462,7 +5056,6 @@
       <c r="C89" s="2" t="n">
         <v>46324</v>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Other</t>
@@ -5483,8 +5076,6 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>Not mentioned</t>
@@ -5508,7 +5099,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5522,7 +5112,6 @@
       <c r="C90" s="2" t="n">
         <v>46325</v>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -5538,15 +5127,11 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>Varies by event; flagship Summit EB $175</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
@@ -5560,19 +5145,24 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Seattle AI Week – AI Summit</t>
+          <t>Cloud, Code &amp; Cocktail Hour | #SeattleAIWeek</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
         <v>46322</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="C91" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MongoDB, Keaton Forrest, MongoDB, Oscar Rivera, KevinTKov</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -5588,18 +5178,26 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>$175 early-bird</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>https://luma.com/34kb3orv</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Seattle AI Week</t>
         </is>
       </c>
       <c r="N91" s="2" t="n">
@@ -5615,24 +5213,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SecureWorld Seattle 2026</t>
+          <t>Running Production with Agents w/ Rootly AI, NVIDIA, Replit, PostHog, &amp; WorkOS</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46330</v>
+        <v>46322</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>46331</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
+        <v>46322</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Rootly, Rootly, PostHog</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5642,20 +5244,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Google, Cohesity, Blue Yonder, OpenAI</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Multiple pass types; current price not publicly surfaced in indexed page</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>https://luma.com/r8sy88tq</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Luma SF</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
@@ -5671,24 +5273,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PASS Data Community Summit West</t>
+          <t>San Francisco Syntax Meetup</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46335</v>
+        <v>46322</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>46337</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
+        <v>46322</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Syntax FM, Syntax FM</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5696,18 +5302,22 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>$1,790–$1,990 for published 2-day ticket</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>https://luma.com/5ng6bniy</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Luma SF</t>
         </is>
       </c>
       <c r="N93" s="2" t="n">
@@ -5723,47 +5333,49 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Microsoft Ignite 2026</t>
+          <t>AI-Driven Threat Investigation with Amazon GuardDuty &amp; AWS Security Hub</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v>46346</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+        <v>46323</v>
+      </c>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Seattle Business and Technology Meetup Group</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>In-person</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Seattle Business and Technology Meetup Group</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://ignite.microsoft.com/en-US/home</t>
+          <t>https://www.meetup.com/seattle-business-and-technology-meetup-group/events/316816197/</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Meetup Seattle - AWS</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
@@ -5779,22 +5391,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloudflare Immerse</t>
+          <t>Agents in NYC</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46346</v>
-      </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" t="inlineStr"/>
+        <v>46323</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Datadog, Albert Zhao, Datadog</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5804,20 +5422,24 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
+          <t>https://luma.com/agentsinnyc</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Luma NYC</t>
         </is>
       </c>
       <c r="N95" s="2" t="n">
@@ -5833,51 +5455,53 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS re:Invent</t>
+          <t>Build a Cloud-Native Foundation for AI with Azure Red Hat OpenShift</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>46360</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
+        <v>46323</v>
+      </c>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Microsoft Reactor Redmond</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Las Vegas</t>
-        </is>
-      </c>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>In-person</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Microsoft Reactor Redmond</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://aws.amazon.com/events/</t>
+          <t>https://www.meetup.com/microsoft-reactor-redmond/events/316854153/</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Meetup Seattle - AWS</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
@@ -5893,59 +5517,3653 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>Git Sum Dim Sum w/ Databricks &amp; Sentry</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sentry, Sentry, Databricks</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>https://luma.com/git-sum</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Luma SF</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Modernize SQL for an AI-ready data estate</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Quadrant Technologies</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Bellevue</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Quadrant Technologies</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/real-time-intelligence-using-microsoft-fabric/events/317075539/</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Meetup Seattle - AWS</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Seattle Designers | Claude Community x PSL: Creative problem solving with AI</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Claude Community Events, Lucas Dickey</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>https://luma.com/claude-448g</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Seattle AI Week</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-2027 Kickoff 🎃</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AWS SBG at University of Washington</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>AWS SBG at University of Washington</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/aws-sbg-at-university-of-washington/events/316964535/</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Meetup Seattle - AWS</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Mexico City</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/mexicocity27/citylanding/page/cityhome</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>IBM Bob TV episode 3: Benchmarking optimization tasks, cost &amp; quality with Bob</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>46330</v>
+      </c>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Data, Cloud and AI in Seattle</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Data, Cloud and AI in Seattle</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/big-data-developers-in-seattle/events/317075384/</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Meetup Seattle - AWS</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SecureWorld Seattle 2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>46330</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>46331</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Bellevue</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Google, Cohesity, Blue Yonder, OpenAI</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Multiple pass types; current price not publicly surfaced in indexed page</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Legacy tracker 2026</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Harnessing Data, AI &amp; Strategic Technologies to Drive Business Performance</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>46331</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>46331</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.co.uk/e/harnessing-data-ai-strategic-technologies-to-drive-business-performance-tickets-2000145093818</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Eventbrite SF - cloud partner</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DevFest Seattle 2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>46333</v>
+      </c>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Google Developer Group (GDG) Seattle</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Google Developer Group (GDG) Seattle</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/gdg-seattle/events/316821635/</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Meetup Seattle - AWS</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PASS Data Community Summit West</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>46335</v>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>46337</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>$1,790–$1,990 for published 2-day ticket</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Legacy tracker 2026</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SaaSify Partner Central Agentic Workshop</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>46338</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>46338</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003698327636</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Eventbrite Seattle - AWS/Microsoft/Google</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>All My Hexes Live in Texas</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>46339</v>
+      </c>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>MaptimeSEA</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Microsoft, Google</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>MaptimeSEA</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/maptimesea/events/317097991/</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Meetup Seattle - AWS</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Microsoft Ignite 2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>46343</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>46346</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>https://ignite.microsoft.com/en-US/home</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Legacy tracker 2026</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SaaSify Partner Central Agentic Workshop</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>46343</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>46343</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Eventbrite SF - cloud partner</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Cloudflare Immerse</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>46346</v>
+      </c>
+      <c r="C111" s="2" t="n"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Legacy tracker 2026</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>NVIDIA GTC Washington, D.C. 2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>46359</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/gtc/events/</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>NVIDIA GTC</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AWS re:Invent</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>46357</v>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>46360</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/events/</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Legacy tracker 2026</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B114" s="2" t="n">
         <v>46357</v>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
+      <c r="C114" s="2" t="n"/>
+      <c r="E114" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t>Google, Dynatrace, Cloudflare</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>Invite/application-based; no public attendee fee</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Legacy tracker 2026</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Legacy tracker 2026</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DEEP DIVE: Scale Faster with Zero Trust</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>46358</v>
+      </c>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>https://events.channelpronetwork.com/deep-dive-scale-faster-with-zero-trust/</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MSP Summit: AI Symposium</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>46365</v>
+      </c>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>MSP Summit / events calendar</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Seattle</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>46365</v>
+      </c>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Utrecht</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/utrecht27/citylanding/page/cityhome</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Toronto</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>46400</v>
+      </c>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/toronto27/citylanding/page/cityhome</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Madrid</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>46401</v>
+      </c>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/madrid27/citylanding/page/cityhome</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Taipei</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>46407</v>
+      </c>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetaipei/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Chicago</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>46420</v>
+      </c>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymechicago/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Sydney</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>46422</v>
+      </c>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymesydney/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Johannesburg</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymejoburg/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Mumbai</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Bengaluru</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ChannelPro DEEP DIVE: Cybersecurity in the Age of AI</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>46434</v>
+      </c>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Milan</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>46436</v>
+      </c>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemilan/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Xchange 2027</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>46453</v>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>46455</v>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>https://event.thechannelco.com/xchange-march/</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Xchange (The Channel Co)</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Channel Partners Conference &amp; Expo 2027</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>46464</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Informa Group PLC</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>The Venetian</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>https://channelpartnersconference.com/</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Channel Partners Conference</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NVIDIA GTC 2027</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>46464</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/gtc/events/</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>NVIDIA GTC</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Stockholm</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>46463</v>
+      </c>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymestockholm/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - New York City</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>46464</v>
+      </c>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - São Paulo</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>46470</v>
+      </c>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymesaopaulo/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Oracle Customer Edge Summit 2027</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>46482</v>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>46484</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/customer-edge-summit/</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Oracle Customer Edge Summit</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Riyadh</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>46484</v>
+      </c>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeriyadh/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Google Cloud Next 2027</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>46489</v>
+      </c>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/next</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Google Cloud Next</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Seoul</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>46491</v>
+      </c>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeseoul/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Tokyo</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetokyo/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Zurich</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymezurich/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Jakarta</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>46499</v>
+      </c>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymejakarta/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Miami</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>46505</v>
+      </c>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemiami/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Copenhagen</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>46506</v>
+      </c>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymecopenhagen/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Montreal</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>46532</v>
+      </c>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemontreal/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Brussels</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>46534</v>
+      </c>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebrussels/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>46539</v>
+      </c>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Houston</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>46540</v>
+      </c>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Tel Aviv</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>46540</v>
+      </c>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetelaviv/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Cisco Live 2027</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>46544</v>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>46548</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Cisco Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2795.00</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ciscolive.com/global.html</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Cisco Live</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Snowflake Summit 2027</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>46545</v>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>46548</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Snowflake, Anthropic</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Host, Speaker</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/summit/</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Snowflake events</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Atlanta</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>46553</v>
+      </c>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeatlanta/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Databricks Data+AI Summit 2027</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>46559</v>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>46562</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.databricks.com/dataaisummit/agenda</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Databricks Data+AI Summit</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour - Osaka</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>46562</v>
+      </c>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Osaka</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeosaka/page/notifyme</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>46623</v>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TechCon 365, DATACON &amp; PWRCON Seattle 2027</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>46643</v>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.techcon365.com/Seattle/</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>TechCon 365 Seattle</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Dreamforce 2027</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>46651</v>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>46653</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.salesforce.com/dreamforce/</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Dreamforce</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MSP Summit 2027, featuring the MSP 501 Awards</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>46657</v>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>46659</v>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>https://technology.informaengage.com/msps27-get-notified</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>MSP Summit / events calendar</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Workday Rising 2027</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>46657</v>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>46660</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>https://rising.workday.com/us.html</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Workday Rising</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Okta Oktane 2027</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>46658</v>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>46660</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>https://www.okta.com/oktane/on-demand/</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Okta Oktane</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>46679</v>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Oracle AI World 2027</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>46685</v>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>46688</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Host, Speaker</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/ai-world/</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Oracle AI World</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P97"/>
+  <autoFilter ref="A1:P161"/>
   <dataValidations count="1">
     <dataValidation sqref="O2:O5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"New,Attending,Skip"</formula1>
@@ -6021,9 +9239,74 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$P$161</definedName>
@@ -5188,8 +5188,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" s="3" t="inlineStr">
         <is>
           <t>https://luma.com/34kb3orv</t>
@@ -5208,7 +5206,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5247,9 +5244,6 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" s="3" t="inlineStr">
         <is>
           <t>https://luma.com/r8sy88tq</t>
@@ -5268,7 +5262,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5307,9 +5300,6 @@
           <t>Salesforce</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" s="3" t="inlineStr">
         <is>
           <t>https://luma.com/5ng6bniy</t>
@@ -5328,7 +5318,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5350,7 +5339,6 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>Virtual</t>
@@ -5361,13 +5349,11 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>Seattle Business and Technology Meetup Group</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/seattle-business-and-technology-meetup-group/events/316816197/</t>
@@ -5386,7 +5372,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5430,8 +5415,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" s="3" t="inlineStr">
         <is>
           <t>https://luma.com/agentsinnyc</t>
@@ -5450,7 +5433,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5472,7 +5454,6 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>Virtual</t>
@@ -5493,7 +5474,6 @@
           <t>Microsoft Reactor Redmond</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/microsoft-reactor-redmond/events/316854153/</t>
@@ -5512,7 +5492,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5556,8 +5535,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" s="3" t="inlineStr">
         <is>
           <t>https://luma.com/git-sum</t>
@@ -5576,7 +5553,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5613,13 +5589,11 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>Quadrant Technologies</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/real-time-intelligence-using-microsoft-fabric/events/317075539/</t>
@@ -5638,7 +5612,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5682,8 +5655,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" s="3" t="inlineStr">
         <is>
           <t>https://luma.com/claude-448g</t>
@@ -5702,7 +5673,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5749,7 +5719,6 @@
           <t>AWS SBG at University of Washington</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/aws-sbg-at-university-of-washington/events/316964535/</t>
@@ -5768,7 +5737,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5795,7 +5763,6 @@
           <t>Mexico City</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -5806,8 +5773,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/mexicocity27/citylanding/page/cityhome</t>
@@ -5826,7 +5791,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5848,7 +5812,6 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>Virtual</t>
@@ -5859,13 +5822,11 @@
           <t>IBM</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>Data, Cloud and AI in Seattle</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/big-data-developers-in-seattle/events/317075384/</t>
@@ -5884,7 +5845,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5949,7 +5909,6 @@
       <c r="C104" s="2" t="n">
         <v>46331</v>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -5970,9 +5929,6 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" s="3" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/harnessing-data-ai-strategic-technologies-to-drive-business-performance-tickets-2000145093818</t>
@@ -5991,7 +5947,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6038,7 +5993,6 @@
           <t>Google Developer Group (GDG) Seattle</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/gdg-seattle/events/316821635/</t>
@@ -6057,7 +6011,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6117,7 +6070,6 @@
       <c r="C107" s="2" t="n">
         <v>46338</v>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -6138,9 +6090,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" s="3" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003698327636</t>
@@ -6159,7 +6108,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6196,13 +6144,11 @@
           <t>Microsoft, Google</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>MaptimeSEA</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/maptimesea/events/317097991/</t>
@@ -6221,7 +6167,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6286,7 +6231,6 @@
       <c r="C110" s="2" t="n">
         <v>46343</v>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -6307,9 +6251,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
       <c r="L110" s="3" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
@@ -6328,7 +6269,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6406,7 +6346,6 @@
           <t>Washington</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>NVIDIA</t>
@@ -6417,8 +6356,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
       <c r="L112" s="3" t="inlineStr">
         <is>
           <t>https://www.nvidia.com/gtc/events/</t>
@@ -6437,7 +6374,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6554,22 +6490,16 @@
         <v>46358</v>
       </c>
       <c r="C115" s="2" t="n"/>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
       <c r="L115" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/deep-dive-scale-faster-with-zero-trust/</t>
@@ -6588,7 +6518,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6600,22 +6529,16 @@
         <v>46365</v>
       </c>
       <c r="C116" s="2" t="n"/>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
       <c r="L116" s="3" t="inlineStr">
         <is>
           <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
@@ -6634,7 +6557,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6661,7 +6583,6 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6672,8 +6593,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
@@ -6692,7 +6611,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6719,7 +6637,6 @@
           <t>Utrecht</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6730,8 +6647,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
       <c r="L118" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/utrecht27/citylanding/page/cityhome</t>
@@ -6750,7 +6665,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6777,7 +6691,6 @@
           <t>Toronto</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6788,8 +6701,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/toronto27/citylanding/page/cityhome</t>
@@ -6808,7 +6719,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6835,7 +6745,6 @@
           <t>Madrid</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6846,8 +6755,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/madrid27/citylanding/page/cityhome</t>
@@ -6866,7 +6773,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6893,7 +6799,6 @@
           <t>Taipei</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6904,8 +6809,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetaipei/page/notifyme</t>
@@ -6924,7 +6827,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6951,7 +6853,6 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6962,8 +6863,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymechicago/page/notifyme</t>
@@ -6982,7 +6881,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7009,7 +6907,6 @@
           <t>Sydney</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7020,8 +6917,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymesydney/page/notifyme</t>
@@ -7040,7 +6935,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7067,7 +6961,6 @@
           <t>Johannesburg</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7078,8 +6971,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymejoburg/page/notifyme</t>
@@ -7098,7 +6989,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7125,7 +7015,6 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7136,8 +7025,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
@@ -7156,7 +7043,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7183,7 +7069,6 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7194,8 +7079,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
@@ -7214,7 +7097,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7226,22 +7108,16 @@
         <v>46434</v>
       </c>
       <c r="C127" s="2" t="n"/>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
@@ -7260,7 +7136,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7287,7 +7162,6 @@
           <t>Milan</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7298,8 +7172,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemilan/page/notifyme</t>
@@ -7318,7 +7190,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7332,18 +7203,11 @@
       <c r="C129" s="2" t="n">
         <v>46455</v>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr">
         <is>
           <t>https://event.thechannelco.com/xchange-march/</t>
@@ -7362,7 +7226,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7396,10 +7259,6 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
       <c r="L130" s="3" t="inlineStr">
         <is>
           <t>https://channelpartnersconference.com/</t>
@@ -7418,7 +7277,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7442,8 +7300,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>NVIDIA</t>
@@ -7454,8 +7310,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr">
         <is>
           <t>https://www.nvidia.com/gtc/events/</t>
@@ -7474,7 +7328,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7501,7 +7354,6 @@
           <t>Stockholm</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7512,8 +7364,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
       <c r="L132" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymestockholm/page/notifyme</t>
@@ -7532,7 +7382,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7559,7 +7408,6 @@
           <t>New York City</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7570,8 +7418,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
@@ -7590,7 +7436,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7617,7 +7462,6 @@
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7628,8 +7472,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
       <c r="L134" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymesaopaulo/page/notifyme</t>
@@ -7648,7 +7490,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7677,7 +7518,6 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>Oracle</t>
@@ -7688,8 +7528,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr">
         <is>
           <t>https://www.oracle.com/customer-edge-summit/</t>
@@ -7708,7 +7546,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7735,7 +7572,6 @@
           <t>Riyadh</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7746,8 +7582,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeriyadh/page/notifyme</t>
@@ -7766,7 +7600,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7788,8 +7621,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>Google</t>
@@ -7800,8 +7631,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr">
         <is>
           <t>https://cloud.google.com/next</t>
@@ -7820,7 +7649,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7847,7 +7675,6 @@
           <t>Seoul</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7858,8 +7685,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
       <c r="L138" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeseoul/page/notifyme</t>
@@ -7878,7 +7703,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7905,7 +7729,6 @@
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7916,8 +7739,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetokyo/page/notifyme</t>
@@ -7936,7 +7757,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7963,7 +7783,6 @@
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7974,8 +7793,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
       <c r="L140" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymezurich/page/notifyme</t>
@@ -7994,7 +7811,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8021,7 +7837,6 @@
           <t>Jakarta</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8032,8 +7847,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymejakarta/page/notifyme</t>
@@ -8052,7 +7865,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8079,7 +7891,6 @@
           <t>Miami</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8090,8 +7901,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
       <c r="L142" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemiami/page/notifyme</t>
@@ -8110,7 +7919,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8137,7 +7945,6 @@
           <t>Copenhagen</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8148,8 +7955,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymecopenhagen/page/notifyme</t>
@@ -8168,7 +7973,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8195,7 +7999,6 @@
           <t>Montreal</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8206,8 +8009,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
       <c r="L144" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemontreal/page/notifyme</t>
@@ -8226,7 +8027,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8253,7 +8053,6 @@
           <t>Brussels</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8264,8 +8063,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebrussels/page/notifyme</t>
@@ -8284,7 +8081,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8296,22 +8092,16 @@
         <v>46539</v>
       </c>
       <c r="C146" s="2" t="n"/>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
       <c r="L146" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
@@ -8330,7 +8120,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8357,7 +8146,6 @@
           <t>Houston</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8368,8 +8156,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
@@ -8388,7 +8174,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8415,7 +8200,6 @@
           <t>Tel Aviv</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8426,8 +8210,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetelaviv/page/notifyme</t>
@@ -8446,7 +8228,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8470,7 +8251,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>Hybrid</t>
@@ -8514,7 +8294,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8538,8 +8317,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>Snowflake, Anthropic</t>
@@ -8550,8 +8327,6 @@
           <t>Host, Speaker</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
       <c r="L150" s="3" t="inlineStr">
         <is>
           <t>https://www.snowflake.com/en/summit/</t>
@@ -8570,7 +8345,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8597,7 +8371,6 @@
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8608,8 +8381,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeatlanta/page/notifyme</t>
@@ -8628,7 +8399,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8652,8 +8422,6 @@
           <t>Bay Area</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>Databricks</t>
@@ -8664,8 +8432,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
       <c r="L152" s="3" t="inlineStr">
         <is>
           <t>https://www.databricks.com/dataaisummit/agenda</t>
@@ -8684,7 +8450,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8711,7 +8476,6 @@
           <t>Osaka</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8722,8 +8486,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeosaka/page/notifyme</t>
@@ -8742,7 +8504,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8754,22 +8515,16 @@
         <v>46623</v>
       </c>
       <c r="C154" s="2" t="n"/>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
       <c r="L154" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
@@ -8788,7 +8543,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8810,8 +8564,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -8822,8 +8574,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
       <c r="L155" s="3" t="inlineStr">
         <is>
           <t>https://www.techcon365.com/Seattle/</t>
@@ -8842,7 +8592,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8866,8 +8615,6 @@
           <t>Bay Area</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>Salesforce</t>
@@ -8878,8 +8625,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" s="3" t="inlineStr">
         <is>
           <t>https://www.salesforce.com/dreamforce/</t>
@@ -8898,7 +8643,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8912,18 +8656,11 @@
       <c r="C157" s="2" t="n">
         <v>46659</v>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
       <c r="L157" s="3" t="inlineStr">
         <is>
           <t>https://technology.informaengage.com/msps27-get-notified</t>
@@ -8942,7 +8679,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8966,8 +8702,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>Workday</t>
@@ -8978,8 +8712,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
       <c r="L158" s="3" t="inlineStr">
         <is>
           <t>https://rising.workday.com/us.html</t>
@@ -8998,7 +8730,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9022,8 +8753,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>Okta</t>
@@ -9034,8 +8763,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
       <c r="L159" s="3" t="inlineStr">
         <is>
           <t>https://www.okta.com/oktane/on-demand/</t>
@@ -9054,7 +8781,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9066,22 +8792,16 @@
         <v>46679</v>
       </c>
       <c r="C160" s="2" t="n"/>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
       <c r="L160" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
@@ -9100,7 +8820,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9129,7 +8848,6 @@
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>Oracle</t>
@@ -9140,8 +8858,6 @@
           <t>Host, Speaker</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
       <c r="L161" s="3" t="inlineStr">
         <is>
           <t>https://www.oracle.com/ai-world/</t>
@@ -9160,7 +8876,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P161"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,17 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$P$161</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -145,6 +143,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:P161" headerRowCount="1">
+  <autoFilter ref="A1:P161"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="Name"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="End Date"/>
+    <tableColumn id="4" name="Organiser/Host"/>
+    <tableColumn id="5" name="Region"/>
+    <tableColumn id="6" name="City"/>
+    <tableColumn id="7" name="Format"/>
+    <tableColumn id="8" name="Companies Attending"/>
+    <tableColumn id="9" name="Role"/>
+    <tableColumn id="10" name="Named Speakers"/>
+    <tableColumn id="11" name="Cost"/>
+    <tableColumn id="12" name="URL"/>
+    <tableColumn id="13" name="Source"/>
+    <tableColumn id="14" name="Date Added"/>
+    <tableColumn id="15" name="Status"/>
+    <tableColumn id="16" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8878,7 +8901,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P161"/>
   <dataValidations count="1">
     <dataValidation sqref="O2:O5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"New,Attending,Skip"</formula1>
@@ -9024,5 +9046,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId138"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -146,8 +146,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:P161" headerRowCount="1">
-  <autoFilter ref="A1:P161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:P143" headerRowCount="1">
+  <autoFilter ref="A1:P143"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Date"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P161"/>
+  <dimension ref="A1:P143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -572,6 +572,11 @@
         <v>45762</v>
       </c>
       <c r="C2" s="2" t="n"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>India</t>
@@ -774,6 +779,11 @@
         <v>46035</v>
       </c>
       <c r="C6" s="2" t="n"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Other</t>
@@ -828,6 +838,11 @@
         <v>46037</v>
       </c>
       <c r="C7" s="2" t="n"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -882,6 +897,11 @@
         <v>46037</v>
       </c>
       <c r="C8" s="2" t="n"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Other</t>
@@ -936,6 +956,11 @@
         <v>46042</v>
       </c>
       <c r="C9" s="2" t="n"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Other</t>
@@ -980,6 +1005,11 @@
         <v>46043</v>
       </c>
       <c r="C10" s="2" t="n"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>New York</t>
@@ -1034,6 +1064,11 @@
         <v>46044</v>
       </c>
       <c r="C11" s="2" t="n"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>India</t>
@@ -1090,6 +1125,11 @@
       <c r="C12" s="2" t="n">
         <v>46050</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Acumatica</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -1146,6 +1186,11 @@
       <c r="C13" s="2" t="n">
         <v>46051</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Dynatrace</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1200,6 +1245,11 @@
         <v>46049</v>
       </c>
       <c r="C14" s="2" t="n"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1254,6 +1304,11 @@
         <v>46063</v>
       </c>
       <c r="C15" s="2" t="n"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>India</t>
@@ -1354,6 +1409,11 @@
         <v>46070</v>
       </c>
       <c r="C17" s="2" t="n"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>India</t>
@@ -1457,6 +1517,11 @@
         <v>46080</v>
       </c>
       <c r="C19" s="2" t="n"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Commvault</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>India</t>
@@ -1564,6 +1629,11 @@
       <c r="C21" s="2" t="n">
         <v>46094</v>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1618,6 +1688,11 @@
         <v>46091</v>
       </c>
       <c r="C22" s="2" t="n"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1674,6 +1749,11 @@
       <c r="C23" s="2" t="n">
         <v>46100</v>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -1781,6 +1861,11 @@
       <c r="C25" s="2" t="n">
         <v>46100</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1837,6 +1922,11 @@
       <c r="C26" s="2" t="n">
         <v>46100</v>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Qualtrics</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -1995,6 +2085,11 @@
       <c r="C29" s="2" t="n">
         <v>46121</v>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2051,6 +2146,11 @@
       <c r="C30" s="2" t="n">
         <v>46126</v>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Texas</t>
@@ -2105,6 +2205,11 @@
         <v>46126</v>
       </c>
       <c r="C31" s="2" t="n"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2156,6 +2261,11 @@
       <c r="C32" s="2" t="n">
         <v>46134</v>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2212,6 +2322,11 @@
       <c r="C33" s="2" t="n">
         <v>46136</v>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2308,38 +2423,48 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ODSC AI East 2026 / Gen AI X Summit</t>
+          <t>IBM Think</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46142</v>
+        <v>46149</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Boston Massachusetts</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>IBM</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>499-1599</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>https://odsc.ai/east/</t>
+          <t>https://www.ibm.com/events/think</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2359,15 +2484,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IBM Think</t>
+          <t>Knowledge 2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>46149</v>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2375,7 +2505,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Boston Massachusetts</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2385,17 +2515,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>https://www.ibm.com/events/think</t>
+          <t>https://www.servicenow.com/events.html</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2415,7 +2545,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Knowledge 2026</t>
+          <t>Team 26</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -2424,6 +2554,11 @@
       <c r="C37" s="2" t="n">
         <v>46149</v>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2431,27 +2566,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>In-person</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>699</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>https://www.servicenow.com/events.html</t>
+          <t>https://events.atlassian.com/team/</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2471,14 +2606,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Team 26</t>
+          <t>SAP Sapphire</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46149</v>
+        <v>46155</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2487,7 +2627,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2497,17 +2637,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>https://events.atlassian.com/team/</t>
+          <t>https://www.sap.com/events.html#global-events</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2527,33 +2667,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAP Sapphire</t>
+          <t>SaaStr AI: ANNUAL x AI Summit</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>SAP</t>
+          <t>In-person</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2563,7 +2698,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>https://www.sap.com/events.html#global-events</t>
+          <t>https://www.saastrannual.com/</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2583,23 +2718,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SaaStr AI: ANNUAL x AI Summit</t>
+          <t>Catalyst by Partnership Leaders</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2609,12 +2739,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>1200-2500</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>https://www.saastrannual.com/</t>
+          <t>https://channelpartnersconference.com/</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2634,33 +2764,48 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Catalyst by Partnership Leaders</t>
+          <t>Dell Technologies World</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46157</v>
+        <v>46163</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Dell</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>In-person</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Dell</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1200-2500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>https://channelpartnersconference.com/</t>
+          <t>https://emit.digital/en/news/tech-events-2026</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2680,14 +2825,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dell Technologies World</t>
+          <t>Zendesk relate</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46163</v>
+        <v>46162</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2696,7 +2846,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2706,17 +2856,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://emit.digital/en/news/tech-events-2026</t>
+          <t>https://www.zendeskrelate.com/event/1ce444c1-4c9b-4b1f-9f54-5e85d97d6a75/zendesk-relate-2026</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2736,25 +2886,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Zendesk relate</t>
+          <t>Informatica World</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Informatica</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>In-person</t>
@@ -2762,7 +2912,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2772,7 +2922,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>https://www.zendeskrelate.com/event/1ce444c1-4c9b-4b1f-9f54-5e85d97d6a75/zendesk-relate-2026</t>
+          <t>https://www.informaticaworld.com/</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2792,18 +2942,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Informatica World</t>
+          <t>SAP Now AI Tour</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>46161</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>46163</v>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2813,7 +2971,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2823,7 +2981,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>https://www.informaticaworld.com/</t>
+          <t>https://www.sap.com/india/events/sapnow.html#apac</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -2843,21 +3001,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SAP Now AI Tour</t>
+          <t>Docusign Momentum 26</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="C45" s="2" t="n"/>
+        <v>46162</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2867,7 +3032,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Docusign</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2877,7 +3042,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>https://www.sap.com/india/events/sapnow.html#apac</t>
+          <t>https://momentum.docusign.com/?c_2080266=https%3A%2F%2Fwww.bing.com%2F</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -2897,23 +3062,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Docusign Momentum 26</t>
+          <t>Cisco Live</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>46163</v>
+        <v>46173</v>
+      </c>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2923,17 +3091,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Docusign</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>https://momentum.docusign.com/?c_2080266=https%3A%2F%2Fwww.bing.com%2F</t>
+          <t>https://www.ciscolive.com/global.html</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -2953,21 +3121,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cisco Live</t>
+          <t>Snowflake Summit 2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C47" s="2" t="n"/>
+        <v>46174</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Moscone Center San Francisco</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2977,17 +3152,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2795</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>https://www.ciscolive.com/global.html</t>
+          <t>https://www.snowflake.com/en/summit/</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3007,23 +3177,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Snowflake Summit 2026</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46177</v>
+        <v>46183</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Moscone Center San Francisco</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3033,12 +3208,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://www.snowflake.com/en/summit/</t>
+          <t>https://www.dashcon.io/</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3058,23 +3238,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>Databricks Data+AI Summit</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46183</v>
+        <v>46191</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3084,17 +3269,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>https://www.dashcon.io/</t>
+          <t>https://www.databricks.com/dataaisummit</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3114,23 +3294,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Databricks Data+AI Summit</t>
+          <t>Pure Accelerate 2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>46191</v>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pure Storage</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3140,12 +3325,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Pure Storage</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/dataaisummit</t>
+          <t>https://www.purestorage.com/accelerate.html</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3165,23 +3355,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pure Accelerate 2026</t>
+          <t>TechMentor &amp; Cybersecurity Live! @ Microsoft HQ</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46189</v>
+        <v>46237</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46191</v>
+        <v>46241</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3191,17 +3386,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pure Storage</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>https://www.purestorage.com/accelerate.html</t>
+          <t>Not publicly listed</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3221,23 +3411,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Product Marketing Alliance</t>
+          <t>AI4</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46190</v>
+        <v>46238</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46191</v>
+        <v>46240</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3247,12 +3437,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>https://world.productmarketingalliance.com/location/seattle/agenda</t>
+          <t>https://ai4.io/</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3272,14 +3462,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sales Enablement Summit</t>
+          <t>AI Agents Seattle – August 2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>46191</v>
+        <v>46245</v>
+      </c>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AI / Claude ecosystem</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3296,14 +3489,14 @@
           <t>In-person</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>https://world.salesenablementcollective.com/location/seattle?utm_source=vendelux.com</t>
+          <t>Not publicly listed</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3323,14 +3516,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TechMentor &amp; Cybersecurity Live! @ Microsoft HQ</t>
+          <t>AI Agents in the Wild: Building, Scaling &amp; Deploying in Production</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>46241</v>
+        <v>46246</v>
+      </c>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Salesforce / AWS</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3339,7 +3535,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3349,7 +3545,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>AWS, Salesforce</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3374,23 +3570,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI4</t>
+          <t>NVIDIA Spark Hack: Seattle</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46238</v>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>46240</v>
+        <v>46248</v>
+      </c>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3398,14 +3597,14 @@
           <t>In-person</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1395</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>https://ai4.io/</t>
+          <t>No public fee listed; approval required</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3425,13 +3624,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Agents Seattle – August 2026</t>
+          <t>ISV Partner Event</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="C56" s="2" t="n"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3449,12 +3653,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Not publicly listed</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3474,13 +3678,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI x Bio Demo Night w/ NVIDIA &amp; Allen Institute for AI</t>
+          <t>MICROSOFT 365, DATA &amp; POWER PLATFORM CONFERENCES</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C57" s="2" t="n"/>
+        <v>46258</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3498,17 +3709,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Not publicly listed; application-based</t>
+          <t>1595-2695</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>https://seattle.aitinkerers.org/p/ai-x-bio-demo-night-w-nvidia-allen-institute-for-ai</t>
+          <t>https://www.techcon365.com/Seattle/</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3528,13 +3739,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ClawCon Seattle</t>
+          <t>TechCon 365, DATACON &amp; PWRCON Seattle 2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C58" s="2" t="n"/>
+        <v>46258</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3550,14 +3768,14 @@
           <t>In-person</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>https://www.claw-con.com/</t>
+          <t>$1,825–$2,995 currently, depending on pass</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3577,36 +3795,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Games &amp; AI Meetup / Co-hosted by AWS</t>
+          <t>Vmware Explore</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46245</v>
+        <v>46265</v>
       </c>
       <c r="C59" s="2" t="n"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Vmware</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>In-person</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Not publicly listed; currently waitlist</t>
+          <t>VMware</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.vmware.com/explore?view=all</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3626,13 +3844,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>New Tech Seattle – August 2026 Meetup</t>
+          <t>AWS Marketplace Seller Forum</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C60" s="2" t="n"/>
+        <v>46266</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3640,7 +3865,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3648,14 +3873,19 @@
           <t>In-person</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>$20 advance / $27 day-of</t>
+          <t>Invite only event</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>https://www.newtechnorthwest.com/new-tech-events/new-tech-seattle-august-2026-meetup/</t>
+          <t>https://aws.amazon.com/marketplace/resources/events/seller-conference</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3675,13 +3905,18 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Agents in the Wild: Building, Scaling &amp; Deploying in Production</t>
+          <t>AI, Zero Trust &amp; Enterprise Resilience in the Age of Continuous Disruption</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46246</v>
+        <v>46275</v>
       </c>
       <c r="C61" s="2" t="n"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Intuit / Oracle</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3699,7 +3934,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>AWS, Salesforce</t>
+          <t>Oracle, Intuit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3724,13 +3959,18 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NVIDIA Spark Hack: Seattle</t>
+          <t>CISOMeet Seattle</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46248</v>
+        <v>46275</v>
       </c>
       <c r="C62" s="2" t="n"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3738,7 +3978,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3748,12 +3988,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>No public fee listed; approval required</t>
+          <t>No public fee listed; CISO/Sr. InfoSec qualification</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -3773,23 +4013,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SISO Leadership Conference 2026</t>
+          <t>World Forum</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>46254</v>
+        <v>46275</v>
+      </c>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3797,9 +4040,14 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Not publicly listed</t>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.servicenow.com/events/world-forum.html</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -3819,23 +4067,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Keiretsu Investor Capital Expo</t>
+          <t>Dreamforce 2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46253</v>
+        <v>46280</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46254</v>
+        <v>46282</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3843,9 +4096,14 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Not publicly listed; accredited-investor access</t>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.salesforce.com/dreamforce/?d=pb</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -3865,13 +4123,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ISV Partner Event</t>
+          <t>Amazon Accelerate 2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="C65" s="2" t="n"/>
+        <v>46287</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Amazon / AWS ecosystem</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -3889,12 +4154,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Price not publicly surfaced; $100 early-bird discount through Aug 8</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -3914,21 +4179,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Seattle – Claude Touch Grass Summer Social</t>
+          <t>Okta Octane</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="C66" s="2" t="n"/>
+        <v>46287</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3938,12 +4210,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Free</t>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>https://security.world/event/okta-oktane-2026/</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -3963,14 +4235,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MICROSOFT 365, DATA &amp; POWER PLATFORM CONFERENCES</t>
+          <t>IA40 Summit 2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46258</v>
+        <v>46294</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>46262</v>
+        <v>46295</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AI ecosystem / Microsoft / AWS / Databricks</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3989,17 +4266,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Microsoft, AWS, Databricks</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1595-2695</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>https://www.techcon365.com/Seattle/</t>
+          <t>Invite-only / no public fee</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4019,14 +4291,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TechCon 365, DATACON &amp; PWRCON Seattle 2026</t>
+          <t>Build with Gemini – Seattle</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>46262</v>
+        <v>46295</v>
+      </c>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -4045,12 +4320,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>$1,825–$2,995 currently, depending on pass</t>
+          <t>Free / complimentary</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4070,31 +4345,41 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vmware Explore</t>
+          <t>Official Cybersecurity Summit – Seattle/Bellevue</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46265</v>
+        <v>46296</v>
       </c>
       <c r="C69" s="2" t="n"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>IBM / Cybersecurity ecosystem</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Bellevue</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>In-person</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>VMware</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>https://www.vmware.com/explore?view=all</t>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>$250 standard admission</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4114,43 +4399,48 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Marketplace Seller Forum</t>
+          <t>SAP Connect</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46266</v>
+        <v>46300</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>46267</v>
+        <v>46302</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>In-person</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Invite only event</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>https://aws.amazon.com/marketplace/resources/events/seller-conference</t>
+          <t>https://www.sap.com/events.html#global-events</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4170,21 +4460,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI, Zero Trust &amp; Enterprise Resilience in the Age of Continuous Disruption</t>
+          <t>Cypher 2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C71" s="2" t="n"/>
+        <v>46301</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46303</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4192,14 +4484,14 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Oracle, Intuit</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Not publicly listed</t>
+          <t>7000 (INR)</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>https://kripeshadwani.com/best-tech-events-in-india/#ai-impact-summit-2026</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4219,21 +4511,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CISOMeet Seattle</t>
+          <t>World Forum</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46275</v>
+        <v>46301</v>
       </c>
       <c r="C72" s="2" t="n"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4243,12 +4540,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>No public fee listed; CISO/Sr. InfoSec qualification</t>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.servicenow.com/events/world-forum.html</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4268,21 +4565,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Leading Through AI: From Adoption to Impact</t>
+          <t>Workday Rising</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C73" s="2" t="n"/>
+        <v>46307</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4290,9 +4594,19 @@
           <t>In-person</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>From $299</t>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>https://rising.workday.com/us.html?locale=enus&amp;aud=wd&amp;stage=any&amp;size=all&amp;pblr=soc&amp;pnpnt=pp0&amp;assettype=ev&amp;productfocus=wd&amp;utm_medium=orso&amp;utm_source=osim&amp;reference=emma&amp;step=step1_default</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4312,21 +4626,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mobile Future Forward 2026 – Quantumverse</t>
+          <t>TechCrunch Disrupt 2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C74" s="2" t="n"/>
+        <v>46308</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46310</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4336,7 +4652,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Not publicly surfaced</t>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/events/tc-disrupt-2026/</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4356,21 +4677,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>World Forum</t>
+          <t>ElevateIT Seattle Technology Summit 2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46275</v>
+        <v>46309</v>
       </c>
       <c r="C75" s="2" t="n"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Nutanix / Enterprise IT ecosystem</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4380,12 +4706,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>https://www.servicenow.com/events/world-forum.html</t>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Not publicly listed</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4405,14 +4731,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dreamforce 2026</t>
+          <t>Cloudflare Connect</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46280</v>
+        <v>46314</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>46282</v>
+        <v>46317</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4431,12 +4762,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com/dreamforce/?d=pb</t>
+          <t>https://www.cloudflare.com/en-gb/lp/cloudflare-connect-2026/</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4456,23 +4787,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Amazon Accelerate 2026</t>
+          <t>Oracle AI World</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46287</v>
+        <v>46321</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46289</v>
+        <v>46324</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4482,12 +4818,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Price not publicly surfaced; $100 early-bird discount through Aug 8</t>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/ai-world/</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4507,23 +4848,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Okta Octane</t>
+          <t>Seattle AI Week 2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46287</v>
+        <v>46321</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>46289</v>
+        <v>46325</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Multi-vendor / AI ecosystem</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4531,14 +4877,9 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>https://security.world/event/okta-oktane-2026/</t>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Varies by event; flagship Summit EB $175</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -4558,23 +4899,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IA40 Summit 2026</t>
+          <t>Agents in NYC</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46294</v>
+        <v>46323</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>46295</v>
+        <v>46323</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Datadog, Albert Zhao, Datadog</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4584,17 +4930,24 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Microsoft, AWS, Databricks</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Invite-only / no public fee</t>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>https://luma.com/agentsinnyc</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Luma NYC</t>
         </is>
       </c>
       <c r="N79" s="2" t="n">
@@ -4605,45 +4958,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Build with Gemini – Seattle</t>
+          <t>Microsoft AI Tour - Mexico City</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46295</v>
+        <v>46324</v>
       </c>
       <c r="C80" s="2" t="n"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Free / complimentary</t>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/mexicocity27/citylanding/page/cityhome</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
@@ -4654,17 +5016,25 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Official Cybersecurity Summit – Seattle/Bellevue</t>
+          <t>SecureWorld Seattle 2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C81" s="2" t="n"/>
+        <v>46330</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46331</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OpenAI / Google Cloud / Cohesity / Blue Yonder</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -4682,12 +5052,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Google, Cohesity, Blue Yonder, OpenAI</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>$250 standard admission</t>
+          <t>Multiple pass types; current price not publicly surfaced in indexed page</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -4707,48 +5077,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SAP Connect</t>
+          <t>2026 ChannelPro DEFEND: Anaheim</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46300</v>
+        <v>46335</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>46302</v>
+        <v>46336</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ChannelPro Network</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Las Vegas</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://www.sap.com/events.html#global-events</t>
+          <t>https://events.channelpronetwork.com/2026-channelpro-defend-anaheim/</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
@@ -4759,27 +5120,33 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cypher 2026</t>
+          <t>PASS Data Community Summit West</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46301</v>
+        <v>46335</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>46303</v>
+        <v>46337</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Data / Cloud ecosystem</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4789,12 +5156,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>7000 (INR)</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>https://kripeshadwani.com/best-tech-events-in-india/#ai-impact-summit-2026</t>
+          <t>$1,790–$1,990 for published 2-day ticket</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -4814,21 +5176,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>World Forum</t>
+          <t>SaaSify Partner Central Agentic Workshop</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="C84" s="2" t="n"/>
+        <v>46338</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>46338</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4838,17 +5203,20 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>https://www.servicenow.com/events/world-forum.html</t>
+          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003698327636</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Eventbrite Seattle - AWS/Microsoft/Google</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
@@ -4859,27 +5227,33 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Workday Rising</t>
+          <t>Microsoft Ignite 2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46307</v>
+        <v>46343</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>46310</v>
+        <v>46346</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4889,17 +5263,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>https://rising.workday.com/us.html?locale=enus&amp;aud=wd&amp;stage=any&amp;size=all&amp;pblr=soc&amp;pnpnt=pp0&amp;assettype=ev&amp;productfocus=wd&amp;utm_medium=orso&amp;utm_source=osim&amp;reference=emma&amp;step=step1_default</t>
+          <t>https://ignite.microsoft.com/en-US/home</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -4919,15 +5288,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TechCrunch Disrupt 2026</t>
+          <t>SaaSify Partner Central Agentic Workshop</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46308</v>
+        <v>46343</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>46310</v>
-      </c>
+        <v>46343</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -4943,19 +5313,22 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/events/tc-disrupt-2026/</t>
+          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Eventbrite SF - cloud partner</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
@@ -4966,25 +5339,31 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ElevateIT Seattle Technology Summit 2026</t>
+          <t>Cloudflare Immerse</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46309</v>
+        <v>46346</v>
       </c>
       <c r="C87" s="2" t="n"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4994,12 +5373,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Not publicly listed</t>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5019,43 +5398,51 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloudflare Connect</t>
+          <t>NVIDIA GTC Washington, D.C. 2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46314</v>
+        <v>46356</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>46317</v>
+        <v>46359</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://www.cloudflare.com/en-gb/lp/cloudflare-connect-2026/</t>
+          <t>https://www.nvidia.com/gtc/events/</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>NVIDIA GTC</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
@@ -5066,18 +5453,24 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Oracle AI World</t>
+          <t>AWS re:Invent</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46321</v>
+        <v>46357</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>46324</v>
+        <v>46360</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -5096,7 +5489,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5106,7 +5499,7 @@
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>https://www.oracle.com/ai-world/</t>
+          <t>https://aws.amazon.com/events/</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -5126,14 +5519,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Seattle AI Week 2026</t>
+          <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46321</v>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v>46325</v>
+        <v>46357</v>
+      </c>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Google Cloud / Cloudflare / Dynatrace</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -5150,9 +5546,14 @@
           <t>In-person</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Google, Dynatrace, Cloudflare</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Varies by event; flagship Summit EB $175</t>
+          <t>Invite/application-based; no public attendee fee</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5172,53 +5573,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud, Code &amp; Cocktail Hour | #SeattleAIWeek</t>
+          <t>MSP Summit: AI Symposium</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>MongoDB, Keaton Forrest, MongoDB, Oscar Rivera, KevinTKov</t>
-        </is>
-      </c>
+        <v>46365</v>
+      </c>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MongoDB</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>https://luma.com/34kb3orv</t>
+          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Seattle AI Week</t>
+          <t>MSP Summit / events calendar</t>
         </is>
       </c>
       <c r="N91" s="2" t="n">
@@ -5229,52 +5614,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Running Production with Agents w/ Rootly AI, NVIDIA, Replit, PostHog, &amp; WorkOS</t>
+          <t>Microsoft AI Tour - Seattle</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v>46322</v>
-      </c>
+        <v>46365</v>
+      </c>
+      <c r="C92" s="2" t="n"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Rootly, Rootly, PostHog</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://luma.com/r8sy88tq</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Luma SF</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
@@ -5285,52 +5672,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>San Francisco Syntax Meetup</t>
+          <t>Microsoft AI Tour - Utrecht</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v>46322</v>
-      </c>
+        <v>46366</v>
+      </c>
+      <c r="C93" s="2" t="n"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Syntax FM, Syntax FM</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>https://luma.com/5ng6bniy</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/utrecht27/citylanding/page/cityhome</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Luma SF</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N93" s="2" t="n">
@@ -5341,50 +5730,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Investigation with Amazon GuardDuty &amp; AWS Security Hub</t>
+          <t>Microsoft AI Tour - Toronto</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46323</v>
+        <v>46400</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Seattle Business and Technology Meetup Group</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Seattle Business and Technology Meetup Group</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/seattle-business-and-technology-meetup-group/events/316816197/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/toronto27/citylanding/page/cityhome</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Meetup Seattle - AWS</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
@@ -5395,42 +5788,37 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Agents in NYC</t>
+          <t>Microsoft AI Tour - Madrid</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v>46323</v>
-      </c>
+        <v>46401</v>
+      </c>
+      <c r="C95" s="2" t="n"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Datadog, Albert Zhao, Datadog</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5438,14 +5826,16 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>https://luma.com/agentsinnyc</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/madrid27/citylanding/page/cityhome</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Luma NYC</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N95" s="2" t="n">
@@ -5456,32 +5846,34 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Build a Cloud-Native Foundation for AI with Azure Red Hat OpenShift</t>
+          <t>Microsoft AI Tour - Taipei</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46323</v>
+        <v>46407</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Microsoft Reactor Redmond</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -5492,19 +5884,16 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Microsoft Reactor Redmond</t>
-        </is>
-      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/microsoft-reactor-redmond/events/316854153/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetaipei/page/notifyme</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Meetup Seattle - AWS</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
@@ -5515,57 +5904,44 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Git Sum Dim Sum w/ Databricks &amp; Sentry</t>
+          <t>2027 ChannelPro DEFEND: Orlando</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46323</v>
+        <v>46413</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>46323</v>
+        <v>46414</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sentry, Sentry, Databricks</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>https://luma.com/git-sum</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-defend-orlando/</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Luma SF</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N97" s="2" t="n">
@@ -5576,55 +5952,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Modernize SQL for an AI-ready data estate</t>
+          <t>Microsoft AI Tour - Chicago</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46323</v>
+        <v>46420</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Quadrant Technologies</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bellevue</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Quadrant Technologies</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/real-time-intelligence-using-microsoft-fabric/events/317075539/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymechicago/page/notifyme</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Meetup Seattle - AWS</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
@@ -5635,42 +6010,37 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Seattle Designers | Claude Community x PSL: Creative problem solving with AI</t>
+          <t>Microsoft AI Tour - Sydney</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>46323</v>
-      </c>
+        <v>46422</v>
+      </c>
+      <c r="C99" s="2" t="n"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Claude Community Events, Lucas Dickey</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5678,14 +6048,16 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>https://luma.com/claude-448g</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymesydney/page/notifyme</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Seattle AI Week</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N99" s="2" t="n">
@@ -5696,40 +6068,37 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-2027 Kickoff 🎃</t>
+          <t>Microsoft AI Tour - Johannesburg</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46324</v>
+        <v>46428</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AWS SBG at University of Washington</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5737,19 +6106,16 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>AWS SBG at University of Washington</t>
-        </is>
-      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/aws-sbg-at-university-of-washington/events/316964535/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymejoburg/page/notifyme</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Meetup Seattle - AWS</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
@@ -5760,15 +6126,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Mexico City</t>
+          <t>Microsoft AI Tour - Mumbai</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46324</v>
+        <v>46428</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" t="inlineStr">
@@ -5778,14 +6145,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mexico City</t>
-        </is>
-      </c>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -5796,9 +6164,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/mexicocity27/citylanding/page/cityhome</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -5814,50 +6184,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IBM Bob TV episode 3: Benchmarking optimization tasks, cost &amp; quality with Bob</t>
+          <t>Microsoft AI Tour - Bengaluru</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46330</v>
+        <v>46433</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Data, Cloud and AI in Seattle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Data, Cloud and AI in Seattle</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/big-data-developers-in-seattle/events/317075384/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Meetup Seattle - AWS</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N102" s="2" t="n">
@@ -5868,47 +6242,46 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SecureWorld Seattle 2026</t>
+          <t>ChannelPro DEEP DIVE: Cybersecurity in the Age of AI</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46330</v>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>46331</v>
+        <v>46434</v>
+      </c>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChannelPro Network</t>
+        </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Bellevue</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Google, Cohesity, Blue Yonder, OpenAI</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Multiple pass types; current price not publicly surfaced in indexed page</t>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N103" s="2" t="n">
@@ -5919,47 +6292,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Harnessing Data, AI &amp; Strategic Technologies to Drive Business Performance</t>
+          <t>Microsoft AI Tour - Milan</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46331</v>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v>46331</v>
+        <v>46436</v>
+      </c>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.co.uk/e/harnessing-data-ai-strategic-technologies-to-drive-business-performance-tickets-2000145093818</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemilan/page/notifyme</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Eventbrite SF - cloud partner</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N104" s="2" t="n">
@@ -5970,60 +6350,44 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevFest Seattle 2026</t>
+          <t>2027 ChannelPro LIVE: Nashville</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46333</v>
-      </c>
-      <c r="C105" s="2" t="n"/>
+        <v>46448</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>46449</v>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Google Developer Group (GDG) Seattle</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Google Developer Group (GDG) Seattle</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/gdg-seattle/events/316821635/</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-live-nashville/</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Meetup Seattle - AWS</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N105" s="2" t="n">
@@ -6034,42 +6398,44 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PASS Data Community Summit West</t>
+          <t>Xchange 2027</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46335</v>
+        <v>46453</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>46337</v>
+        <v>46455</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>The Channel Company</t>
+        </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>$1,790–$1,990 for published 2-day ticket</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>https://event.thechannelco.com/xchange-march/</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Xchange (The Channel Co)</t>
         </is>
       </c>
       <c r="N106" s="2" t="n">
@@ -6080,47 +6446,52 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SaaSify Partner Central Agentic Workshop</t>
+          <t>Channel Partners Conference &amp; Expo 2027</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46338</v>
+        <v>46461</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>46338</v>
+        <v>46464</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Informa Group PLC</t>
+        </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>The Venetian</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003698327636</t>
+          <t>https://channelpartnersconference.com/</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Eventbrite Seattle - AWS/Microsoft/Google</t>
+          <t>Channel Partners Conference</t>
         </is>
       </c>
       <c r="N107" s="2" t="n">
@@ -6131,55 +6502,52 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>All My Hexes Live in Texas</t>
+          <t>NVIDIA GTC 2027</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46339</v>
-      </c>
-      <c r="C108" s="2" t="n"/>
+        <v>46461</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>46464</v>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MaptimeSEA</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Microsoft, Google</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>MaptimeSEA</t>
-        </is>
-      </c>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/maptimesea/events/317097991/</t>
+          <t>https://www.nvidia.com/gtc/events/</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Meetup Seattle - AWS</t>
+          <t>NVIDIA GTC</t>
         </is>
       </c>
       <c r="N108" s="2" t="n">
@@ -6190,47 +6558,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Microsoft Ignite 2026</t>
+          <t>Microsoft AI Tour - Stockholm</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v>46346</v>
+        <v>46463</v>
+      </c>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>https://ignite.microsoft.com/en-US/home</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymestockholm/page/notifyme</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N109" s="2" t="n">
@@ -6241,47 +6616,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SaaSify Partner Central Agentic Workshop</t>
+          <t>Microsoft AI Tour - New York City</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>46343</v>
+        <v>46464</v>
+      </c>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>AWS</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Eventbrite SF - cloud partner</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N110" s="2" t="n">
@@ -6292,45 +6674,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cloudflare Immerse</t>
+          <t>Microsoft AI Tour - São Paulo</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46346</v>
+        <v>46470</v>
       </c>
       <c r="C111" s="2" t="n"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymesaopaulo/page/notifyme</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N111" s="2" t="n">
@@ -6341,22 +6732,23 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NVIDIA GTC Washington, D.C. 2026</t>
+          <t>Oracle Customer Edge Summit 2027</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46356</v>
+        <v>46482</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>46359</v>
+        <v>46484</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6366,12 +6758,13 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Washington</t>
-        </is>
-      </c>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6379,14 +6772,16 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>https://www.nvidia.com/gtc/events/</t>
+          <t>https://www.oracle.com/customer-edge-summit/</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>NVIDIA GTC</t>
+          <t>Oracle Customer Edge Summit</t>
         </is>
       </c>
       <c r="N112" s="2" t="n">
@@ -6397,52 +6792,46 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AWS re:Invent</t>
+          <t>ChannelPro DEEP DIVE: Perfecting Your Tool Stack</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v>46360</v>
+        <v>46483</v>
+      </c>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ChannelPro Network</t>
+        </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Las Vegas</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" s="3" t="inlineStr">
         <is>
-          <t>https://aws.amazon.com/events/</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N113" s="2" t="n">
@@ -6453,45 +6842,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
+          <t>Microsoft AI Tour - Riyadh</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46357</v>
+        <v>46484</v>
       </c>
       <c r="C114" s="2" t="n"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Google, Dynatrace, Cloudflare</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Invite/application-based; no public attendee fee</t>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeriyadh/page/notifyme</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N114" s="2" t="n">
@@ -6502,35 +6900,50 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DEEP DIVE: Scale Faster with Zero Trust</t>
+          <t>Google Cloud Next 2027</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46358</v>
+        <v>46489</v>
       </c>
       <c r="C115" s="2" t="n"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/deep-dive-scale-faster-with-zero-trust/</t>
+          <t>https://cloud.google.com/next</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
+          <t>Google Cloud Next</t>
         </is>
       </c>
       <c r="N115" s="2" t="n">
@@ -6541,35 +6954,44 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MSP Summit: AI Symposium</t>
+          <t>2027 ChannelPro LIVE: Chicago</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46365</v>
-      </c>
-      <c r="C116" s="2" t="n"/>
+        <v>46490</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>46491</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChannelPro Network</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-live-chicago/</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>MSP Summit / events calendar</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N116" s="2" t="n">
@@ -6580,15 +7002,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Seattle</t>
+          <t>Microsoft AI Tour - Seoul</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46365</v>
+        <v>46491</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" t="inlineStr">
@@ -6598,14 +7021,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6616,9 +7040,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeseoul/page/notifyme</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -6634,15 +7060,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Utrecht</t>
+          <t>Microsoft AI Tour - Tokyo</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46366</v>
+        <v>46492</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" t="inlineStr">
@@ -6657,9 +7084,10 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Utrecht</t>
-        </is>
-      </c>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6670,9 +7098,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/utrecht27/citylanding/page/cityhome</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetokyo/page/notifyme</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -6688,15 +7118,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Toronto</t>
+          <t>Microsoft AI Tour - Zurich</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46400</v>
+        <v>46492</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" t="inlineStr">
@@ -6711,9 +7142,10 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Toronto</t>
-        </is>
-      </c>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6724,9 +7156,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/toronto27/citylanding/page/cityhome</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymezurich/page/notifyme</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -6742,15 +7176,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Madrid</t>
+          <t>Microsoft AI Tour - Jakarta</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46401</v>
+        <v>46499</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" t="inlineStr">
@@ -6765,9 +7200,10 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Madrid</t>
-        </is>
-      </c>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6778,9 +7214,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/madrid27/citylanding/page/cityhome</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymejakarta/page/notifyme</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -6796,15 +7234,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Taipei</t>
+          <t>Microsoft AI Tour - Miami</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46407</v>
+        <v>46505</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" t="inlineStr">
@@ -6819,9 +7258,10 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Taipei</t>
-        </is>
-      </c>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6832,9 +7272,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetaipei/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemiami/page/notifyme</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -6850,15 +7292,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Chicago</t>
+          <t>Microsoft AI Tour - Copenhagen</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46420</v>
+        <v>46506</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" t="inlineStr">
@@ -6873,9 +7316,10 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chicago</t>
-        </is>
-      </c>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6886,9 +7330,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymechicago/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymecopenhagen/page/notifyme</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -6904,20 +7350,23 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Sydney</t>
+          <t>2027 ChannelPro DEFEND: New Jersey</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46422</v>
-      </c>
-      <c r="C123" s="2" t="n"/>
+        <v>46510</v>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>46511</v>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6925,29 +7374,20 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Sydney</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymesydney/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-defend-new-jersey/</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N123" s="2" t="n">
@@ -6958,15 +7398,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Johannesburg</t>
+          <t>Microsoft AI Tour - Montreal</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46428</v>
+        <v>46532</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" t="inlineStr">
@@ -6981,9 +7422,10 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
-        </is>
-      </c>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -6994,9 +7436,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymejoburg/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemontreal/page/notifyme</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -7012,15 +7456,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Mumbai</t>
+          <t>Microsoft AI Tour - Brussels</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46428</v>
+        <v>46534</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" t="inlineStr">
@@ -7030,14 +7475,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7048,9 +7494,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebrussels/page/notifyme</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -7066,50 +7514,46 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Bengaluru</t>
+          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46433</v>
+        <v>46539</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N126" s="2" t="n">
@@ -7120,35 +7564,54 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Cybersecurity in the Age of AI</t>
+          <t>Microsoft AI Tour - Houston</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46434</v>
+        <v>46540</v>
       </c>
       <c r="C127" s="2" t="n"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N127" s="2" t="n">
@@ -7159,15 +7622,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Milan</t>
+          <t>Microsoft AI Tour - Tel Aviv</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46436</v>
+        <v>46540</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" t="inlineStr">
@@ -7182,9 +7646,10 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Milan</t>
-        </is>
-      </c>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7195,9 +7660,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemilan/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetelaviv/page/notifyme</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -7213,32 +7680,64 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Xchange 2027</t>
+          <t>Cisco Live 2027</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46453</v>
+        <v>46544</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>46455</v>
+        <v>46548</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Cisco Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2795.00</t>
+        </is>
+      </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>https://event.thechannelco.com/xchange-march/</t>
+          <t>https://www.ciscolive.com/global.html</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Xchange (The Channel Co)</t>
+          <t>Cisco Live</t>
         </is>
       </c>
       <c r="N129" s="2" t="n">
@@ -7249,47 +7748,52 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Channel Partners Conference &amp; Expo 2027</t>
+          <t>Snowflake Summit 2027</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46461</v>
+        <v>46545</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>46464</v>
+        <v>46548</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Informa Group PLC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>The Venetian</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Snowflake, Anthropic</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Host, Speaker</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>https://channelpartnersconference.com/</t>
+          <t>https://www.snowflake.com/en/summit/</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Channel Partners Conference</t>
+          <t>Snowflake events</t>
         </is>
       </c>
       <c r="N130" s="2" t="n">
@@ -7300,22 +7804,21 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NVIDIA GTC 2027</t>
+          <t>Microsoft AI Tour - Atlanta</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C131" s="2" t="n">
-        <v>46464</v>
-      </c>
+        <v>46553</v>
+      </c>
+      <c r="C131" s="2" t="n"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7323,9 +7826,15 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7333,14 +7842,16 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>https://www.nvidia.com/gtc/events/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeatlanta/page/notifyme</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>NVIDIA GTC</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N131" s="2" t="n">
@@ -7351,35 +7862,35 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Stockholm</t>
+          <t>Databricks Data+AI Summit 2027</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>46463</v>
-      </c>
-      <c r="C132" s="2" t="n"/>
+        <v>46559</v>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>46562</v>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7387,14 +7898,16 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymestockholm/page/notifyme</t>
+          <t>https://www.databricks.com/dataaisummit/agenda</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Databricks Data+AI Summit</t>
         </is>
       </c>
       <c r="N132" s="2" t="n">
@@ -7405,15 +7918,16 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - New York City</t>
+          <t>Microsoft AI Tour - Osaka</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>46464</v>
+        <v>46562</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" t="inlineStr">
@@ -7423,14 +7937,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>New York City</t>
-        </is>
-      </c>
+          <t>Osaka</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -7441,9 +7956,11 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeosaka/page/notifyme</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -7459,20 +7976,23 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - São Paulo</t>
+          <t>2027 ChannelPro LIVE: Baltimore</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>46470</v>
-      </c>
-      <c r="C134" s="2" t="n"/>
+        <v>46609</v>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>46610</v>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7480,29 +8000,20 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymesaopaulo/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-live-baltimore/</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N134" s="2" t="n">
@@ -7513,52 +8024,46 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Oracle Customer Edge Summit 2027</t>
+          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>46482</v>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>46484</v>
-      </c>
+        <v>46623</v>
+      </c>
+      <c r="C135" s="2" t="n"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Orlando</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>https://www.oracle.com/customer-edge-summit/</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Oracle Customer Edge Summit</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N135" s="2" t="n">
@@ -7569,50 +8074,44 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Riyadh</t>
+          <t>2027 ChannelPro DEFEND: Dallas</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>46484</v>
-      </c>
-      <c r="C136" s="2" t="n"/>
+        <v>46644</v>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>46645</v>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Riyadh</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeriyadh/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N136" s="2" t="n">
@@ -7623,30 +8122,35 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Google Cloud Next 2027</t>
+          <t>Dreamforce 2027</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>46489</v>
-      </c>
-      <c r="C137" s="2" t="n"/>
+        <v>46651</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>46653</v>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7654,14 +8158,16 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>https://cloud.google.com/next</t>
+          <t>https://www.salesforce.com/dreamforce/</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Google Cloud Next</t>
+          <t>Dreamforce</t>
         </is>
       </c>
       <c r="N137" s="2" t="n">
@@ -7672,50 +8178,40 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Seoul</t>
+          <t>MSP Summit 2027, featuring the MSP 501 Awards</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>46491</v>
-      </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+        <v>46657</v>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>46659</v>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Seoul</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeseoul/page/notifyme</t>
+          <t>https://technology.informaengage.com/msps27-get-notified</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>MSP Summit / events calendar</t>
         </is>
       </c>
       <c r="N138" s="2" t="n">
@@ -7726,20 +8222,23 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Tokyo</t>
+          <t>Workday Rising 2027</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>46492</v>
-      </c>
-      <c r="C139" s="2" t="n"/>
+        <v>46657</v>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>46660</v>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7747,14 +8246,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -7762,14 +8258,16 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetokyo/page/notifyme</t>
+          <t>https://rising.workday.com/us.html</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Workday Rising</t>
         </is>
       </c>
       <c r="N139" s="2" t="n">
@@ -7780,20 +8278,23 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Zurich</t>
+          <t>Okta Oktane 2027</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>46492</v>
-      </c>
-      <c r="C140" s="2" t="n"/>
+        <v>46658</v>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>46660</v>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7801,14 +8302,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7816,14 +8314,16 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymezurich/page/notifyme</t>
+          <t>https://www.okta.com/oktane/on-demand/</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Okta Oktane</t>
         </is>
       </c>
       <c r="N140" s="2" t="n">
@@ -7834,20 +8334,23 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Jakarta</t>
+          <t>2027 ChannelPro LIVE: Boston</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>46499</v>
-      </c>
-      <c r="C141" s="2" t="n"/>
+        <v>46665</v>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>46666</v>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7855,29 +8358,20 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Jakarta</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymejakarta/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-live-boston/</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N141" s="2" t="n">
@@ -7888,50 +8382,46 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Miami</t>
+          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>46505</v>
+        <v>46679</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemiami/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N142" s="2" t="n">
@@ -7942,20 +8432,23 @@
           <t>New</t>
         </is>
       </c>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Copenhagen</t>
+          <t>Oracle AI World 2027</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>46506</v>
-      </c>
-      <c r="C143" s="2" t="n"/>
+        <v>46685</v>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>46688</v>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7965,27 +8458,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Copenhagen</t>
-        </is>
-      </c>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Host, Speaker</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymecopenhagen/page/notifyme</t>
+          <t>https://www.oracle.com/ai-world/</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Oracle AI World</t>
         </is>
       </c>
       <c r="N143" s="2" t="n">
@@ -7996,909 +8492,7 @@
           <t>New</t>
         </is>
       </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour - Montreal</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="n">
-        <v>46532</v>
-      </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Montreal</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L144" s="3" t="inlineStr">
-        <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemontreal/page/notifyme</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N144" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour - Brussels</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="n">
-        <v>46534</v>
-      </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Brussels</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebrussels/page/notifyme</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N145" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="n">
-        <v>46539</v>
-      </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>Channel Pro Network</t>
-        </is>
-      </c>
-      <c r="N146" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour - Houston</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="n">
-        <v>46540</v>
-      </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L147" s="3" t="inlineStr">
-        <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N147" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour - Tel Aviv</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="n">
-        <v>46540</v>
-      </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Tel Aviv</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymetelaviv/page/notifyme</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N148" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Cisco Live 2027</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="n">
-        <v>46544</v>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>46548</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Cisco Systems, Inc.</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>2795.00</t>
-        </is>
-      </c>
-      <c r="L149" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ciscolive.com/global.html</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>Cisco Live</t>
-        </is>
-      </c>
-      <c r="N149" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Snowflake Summit 2027</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="n">
-        <v>46545</v>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>46548</v>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Snowflake, Anthropic</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Host, Speaker</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>https://www.snowflake.com/en/summit/</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Snowflake events</t>
-        </is>
-      </c>
-      <c r="N150" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour - Atlanta</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="n">
-        <v>46553</v>
-      </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeatlanta/page/notifyme</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N151" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Databricks Data+AI Summit 2027</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="n">
-        <v>46559</v>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>46562</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L152" s="3" t="inlineStr">
-        <is>
-          <t>https://www.databricks.com/dataaisummit/agenda</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>Databricks Data+AI Summit</t>
-        </is>
-      </c>
-      <c r="N152" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour - Osaka</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="n">
-        <v>46562</v>
-      </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Osaka</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L153" s="3" t="inlineStr">
-        <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymeosaka/page/notifyme</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N153" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="n">
-        <v>46623</v>
-      </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="L154" s="3" t="inlineStr">
-        <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Channel Pro Network</t>
-        </is>
-      </c>
-      <c r="N154" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>TechCon 365, DATACON &amp; PWRCON Seattle 2027</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="n">
-        <v>46643</v>
-      </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>https://www.techcon365.com/Seattle/</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>TechCon 365 Seattle</t>
-        </is>
-      </c>
-      <c r="N155" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Dreamforce 2027</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="n">
-        <v>46651</v>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>46653</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L156" s="3" t="inlineStr">
-        <is>
-          <t>https://www.salesforce.com/dreamforce/</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>Dreamforce</t>
-        </is>
-      </c>
-      <c r="N156" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>MSP Summit 2027, featuring the MSP 501 Awards</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="n">
-        <v>46657</v>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>46659</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
-        <is>
-          <t>https://technology.informaengage.com/msps27-get-notified</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>MSP Summit / events calendar</t>
-        </is>
-      </c>
-      <c r="N157" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Workday Rising 2027</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="n">
-        <v>46657</v>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>46660</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L158" s="3" t="inlineStr">
-        <is>
-          <t>https://rising.workday.com/us.html</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>Workday Rising</t>
-        </is>
-      </c>
-      <c r="N158" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Okta Oktane 2027</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="n">
-        <v>46658</v>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>46660</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L159" s="3" t="inlineStr">
-        <is>
-          <t>https://www.okta.com/oktane/on-demand/</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>Okta Oktane</t>
-        </is>
-      </c>
-      <c r="N159" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="n">
-        <v>46679</v>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>Channel Pro Network</t>
-        </is>
-      </c>
-      <c r="N160" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Oracle AI World 2027</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="n">
-        <v>46685</v>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>46688</v>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Las Vegas</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Host, Speaker</t>
-        </is>
-      </c>
-      <c r="L161" s="3" t="inlineStr">
-        <is>
-          <t>https://www.oracle.com/ai-world/</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>Oracle AI World</t>
-        </is>
-      </c>
-      <c r="N161" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
+      <c r="P143" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -8956,98 +8550,86 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId138"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId126"/>
   </tableParts>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -146,8 +146,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:P68" headerRowCount="1">
-  <autoFilter ref="A1:P68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:P67" headerRowCount="1">
+  <autoFilter ref="A1:P67"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Date"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3728,47 +3728,49 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Channel Partners Conference &amp; Expo 2027</t>
+          <t>Microsoft AI Tour - New York City</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C59" s="2" t="n">
         <v>46464</v>
       </c>
+      <c r="C59" s="2" t="n"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Informa Group PLC</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>The Venetian</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>https://channelpartnersconference.com/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Channel Partners Conference</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N59" s="2" t="n">
@@ -3784,49 +3786,41 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - New York City</t>
+          <t>ChannelPro DEEP DIVE: Perfecting Your Tool Stack</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46464</v>
+        <v>46483</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
@@ -3842,11 +3836,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Perfecting Your Tool Stack</t>
+          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46483</v>
+        <v>46539</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" t="inlineStr">
@@ -3871,7 +3865,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3892,41 +3886,49 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
+          <t>Microsoft AI Tour - Houston</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46539</v>
+        <v>46540</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
@@ -3942,32 +3944,30 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Houston</t>
+          <t>Databricks Data+AI Summit 2027</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46540</v>
-      </c>
-      <c r="C63" s="2" t="n"/>
+        <v>46559</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46562</v>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3979,12 +3979,12 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
+          <t>https://www.databricks.com/dataaisummit/agenda</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Databricks Data+AI Summit</t>
         </is>
       </c>
       <c r="N63" s="2" t="n">
@@ -4000,47 +4000,41 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Databricks Data+AI Summit 2027</t>
+          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46559</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>46562</v>
-      </c>
+        <v>46623</v>
+      </c>
+      <c r="C64" s="2" t="n"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/dataaisummit/agenda</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Databricks Data+AI Summit</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N64" s="2" t="n">
@@ -4056,13 +4050,15 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
+          <t>2027 ChannelPro DEFEND: Dallas</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46623</v>
-      </c>
-      <c r="C65" s="2" t="n"/>
+        <v>46644</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46645</v>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>ChannelPro Network</t>
@@ -4070,22 +4066,18 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4106,39 +4098,47 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2027 ChannelPro DEFEND: Dallas</t>
+          <t>Dreamforce 2027</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46644</v>
+        <v>46651</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46645</v>
+        <v>46653</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
+          <t>https://www.salesforce.com/dreamforce/</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
+          <t>Dreamforce</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
@@ -4154,47 +4154,41 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dreamforce 2027</t>
+          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46651</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>46653</v>
-      </c>
+        <v>46679</v>
+      </c>
+      <c r="C67" s="2" t="n"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com/dreamforce/</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Dreamforce</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
       <c r="N67" s="2" t="n">
@@ -4206,56 +4200,6 @@
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>46679</v>
-      </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>ChannelPro Network</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Channel Pro Network</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4313,11 +4257,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
   </tableParts>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -146,9 +146,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:P67" headerRowCount="1">
-  <autoFilter ref="A1:P67"/>
-  <tableColumns count="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:M68" headerRowCount="1">
+  <autoFilter ref="A1:M68"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Date"/>
     <tableColumn id="3" name="End Date"/>
@@ -162,9 +162,6 @@
     <tableColumn id="11" name="Cost"/>
     <tableColumn id="12" name="URL"/>
     <tableColumn id="13" name="Source"/>
-    <tableColumn id="14" name="Date Added"/>
-    <tableColumn id="15" name="Status"/>
-    <tableColumn id="16" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -459,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -475,9 +472,6 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="45" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,21 +540,6 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Date Added</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -612,14 +591,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -658,14 +629,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -717,14 +680,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -776,14 +731,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -835,14 +782,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -896,14 +835,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -955,14 +886,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1001,14 +924,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1060,14 +975,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1109,14 +1016,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1168,14 +1067,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1229,14 +1120,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1290,14 +1173,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1341,14 +1216,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1402,14 +1269,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1453,14 +1312,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N17" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1512,14 +1363,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1573,14 +1416,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N19" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1629,14 +1464,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1690,14 +1517,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N21" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1746,14 +1565,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1802,14 +1613,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N23" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1856,14 +1659,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1910,14 +1705,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N25" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1964,14 +1751,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N26" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2018,14 +1797,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N27" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2079,14 +1850,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2135,14 +1898,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N29" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2196,14 +1951,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N30" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2250,14 +1997,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N31" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2304,14 +2043,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2358,14 +2089,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N33" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2414,14 +2137,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2470,14 +2185,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N35" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2526,14 +2233,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N36" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2580,14 +2279,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N37" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2634,14 +2325,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N38" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2685,14 +2368,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N39" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2739,14 +2414,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N40" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2790,14 +2457,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N41" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2844,14 +2503,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N42" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2900,14 +2551,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N43" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2949,14 +2592,6 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>New</t>
         </is>
       </c>
     </row>
@@ -3014,15 +2649,6 @@
           <t>Luma NYC</t>
         </is>
       </c>
-      <c r="N45" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3071,14 +2697,6 @@
           <t>Legacy tracker 2026</t>
         </is>
       </c>
-      <c r="N46" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3120,14 +2738,6 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>New</t>
         </is>
       </c>
     </row>
@@ -3177,85 +2787,77 @@
           <t>Eventbrite Seattle - AWS/Microsoft/Google</t>
         </is>
       </c>
-      <c r="N48" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Microsoft Ignite 2026</t>
+          <t>Identity, AI &amp; Cybersecurity: Securing the Enterprise in an Agentic World</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>46346</v>
-      </c>
+        <v>46339</v>
+      </c>
+      <c r="C49" s="2" t="n"/>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Seattle Data, AI &amp; Security</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bellevue</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Seattle Data, AI &amp; Security</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>https://ignite.microsoft.com/en-US/home</t>
+          <t>https://www.meetup.com/seattledataaiandsecurity/events/316481475/</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>New</t>
+          <t>Meetup Seattle - AWS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SaaSify Partner Central Agentic Workshop</t>
+          <t>Microsoft Ignite 2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>46343</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+        <v>46346</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -3273,47 +2875,33 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
+          <t>https://ignite.microsoft.com/en-US/home</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Eventbrite SF - cloud partner</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
+          <t>Legacy tracker 2026</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloudflare Immerse</t>
+          <t>SaaSify Partner Central Agentic Workshop</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46346</v>
-      </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
+        <v>46343</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46343</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -3321,7 +2909,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3331,51 +2919,46 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
+          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>New</t>
+          <t>Eventbrite SF - cloud partner</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
+          <t>Cloudflare Immerse</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46357</v>
+        <v>46346</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Google Cloud / Cloudflare / Dynatrace</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3385,140 +2968,111 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Google, Dynatrace, Cloudflare</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Invite/application-based; no public attendee fee</t>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Legacy tracker 2026</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>New</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MSP Summit: AI Symposium</t>
+          <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46365</v>
+        <v>46357</v>
       </c>
       <c r="C53" s="2" t="n"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Google Cloud / Cloudflare / Dynatrace</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
+          <t>Google, Dynatrace, Cloudflare</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Invite/application-based; no public attendee fee</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>MSP Summit / events calendar</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+          <t>Legacy tracker 2026</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Seattle</t>
+          <t>MSP Summit: AI Symposium</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>46365</v>
       </c>
       <c r="C54" s="2" t="n"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
+          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
+          <t>MSP Summit / events calendar</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Mumbai</t>
+          <t>Microsoft AI Tour - Seattle</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46428</v>
+        <v>46365</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" t="inlineStr">
@@ -3528,12 +3082,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -3551,7 +3105,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3559,24 +3113,15 @@
           <t>Microsoft AI Tour</t>
         </is>
       </c>
-      <c r="N55" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Bengaluru</t>
+          <t>Microsoft AI Tour - Mumbai</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46433</v>
+        <v>46428</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" t="inlineStr">
@@ -3591,7 +3136,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3609,7 +3154,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3617,230 +3162,193 @@
           <t>Microsoft AI Tour</t>
         </is>
       </c>
-      <c r="N56" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Cybersecurity in the Age of AI</t>
+          <t>Microsoft AI Tour - Bengaluru</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46434</v>
+        <v>46433</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Xchange 2027</t>
+          <t>ChannelPro DEEP DIVE: Cybersecurity in the Age of AI</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46453</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>46455</v>
-      </c>
+        <v>46434</v>
+      </c>
+      <c r="C58" s="2" t="n"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The Channel Company</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://event.thechannelco.com/xchange-march/</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Xchange (The Channel Co)</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - New York City</t>
+          <t>Xchange 2027</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46464</v>
-      </c>
-      <c r="C59" s="2" t="n"/>
+        <v>46453</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46455</v>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>The Channel Company</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
+          <t>https://event.thechannelco.com/xchange-march/</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
+          <t>Xchange (The Channel Co)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Perfecting Your Tool Stack</t>
+          <t>Microsoft AI Tour - New York City</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46483</v>
+        <v>46464</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
+          <t>ChannelPro DEEP DIVE: Perfecting Your Tool Stack</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46539</v>
+        <v>46483</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" t="inlineStr">
@@ -3865,7 +3373,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3873,101 +3381,77 @@
           <t>Channel Pro Network</t>
         </is>
       </c>
-      <c r="N61" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Houston</t>
+          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46540</v>
+        <v>46539</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Databricks Data+AI Summit 2027</t>
+          <t>Microsoft AI Tour - Houston</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46559</v>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>46562</v>
-      </c>
+        <v>46540</v>
+      </c>
+      <c r="C63" s="2" t="n"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3979,86 +3463,72 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/dataaisummit/agenda</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Databricks Data+AI Summit</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
+          <t>Microsoft AI Tour</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
+          <t>Databricks Data+AI Summit 2027</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46623</v>
-      </c>
-      <c r="C64" s="2" t="n"/>
+        <v>46559</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46562</v>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
+          <t>https://www.databricks.com/dataaisummit/agenda</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
+          <t>Databricks Data+AI Summit</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2027 ChannelPro DEFEND: Dallas</t>
+          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46644</v>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>46645</v>
-      </c>
+        <v>46623</v>
+      </c>
+      <c r="C65" s="2" t="n"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>ChannelPro Network</t>
@@ -4066,18 +3536,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4085,128 +3559,135 @@
           <t>Channel Pro Network</t>
         </is>
       </c>
-      <c r="N65" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dreamforce 2027</t>
+          <t>2027 ChannelPro DEFEND: Dallas</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46651</v>
+        <v>46644</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46653</v>
+        <v>46645</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com/dreamforce/</t>
+          <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Dreamforce</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
+          <t>Dreamforce 2027</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46679</v>
-      </c>
-      <c r="C67" s="2" t="n"/>
+        <v>46651</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46653</v>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr">
         <is>
+          <t>https://www.salesforce.com/dreamforce/</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Dreamforce</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>46679</v>
+      </c>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ChannelPro Network</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Channel Pro Network</t>
         </is>
       </c>
-      <c r="N67" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="O2:O5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"New,Attending,Skip"</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -4242,7 +3723,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId38"/>
@@ -4257,10 +3738,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51"/>
   </tableParts>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -146,8 +146,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:M68" headerRowCount="1">
-  <autoFilter ref="A1:M68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events" displayName="Events" ref="A1:M71" headerRowCount="1">
+  <autoFilter ref="A1:M71"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Date"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2939,16 +2939,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloudflare Immerse</t>
+          <t>Catalyst Breakfast at Microsoft Ignite</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46346</v>
+        <v>46344</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Partnership Leaders</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2968,43 +2968,46 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
+          <t>https://www.joincatalyst.com/catalyst-breakfast-at-microsoft-ignite</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Partnership Leaders events</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
+          <t>Cloudflare Immerse</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46357</v>
+        <v>46346</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Google Cloud / Cloudflare / Dynatrace</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3014,12 +3017,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Google, Dynatrace, Cloudflare</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Invite/application-based; no public attendee fee</t>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3031,146 +3034,135 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MSP Summit: AI Symposium</t>
+          <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46365</v>
+        <v>46357</v>
       </c>
       <c r="C54" s="2" t="n"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Google Cloud / Cloudflare / Dynatrace</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
+          <t>Google, Dynatrace, Cloudflare</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Invite/application-based; no public attendee fee</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>MSP Summit / events calendar</t>
+          <t>Legacy tracker 2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Seattle</t>
+          <t>CMA Power Circles</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46365</v>
+        <v>46358</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Channel Marketing Association</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
+          <t>https://www.channelmarketingassociation.com/industry-events</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Marketing Association events</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Mumbai</t>
+          <t>MSP Summit: AI Symposium</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46428</v>
+        <v>46365</v>
       </c>
       <c r="C56" s="2" t="n"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
+          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>MSP Summit / events calendar</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Bengaluru</t>
+          <t>Microsoft AI Tour - Seattle</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46433</v>
+        <v>46365</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" t="inlineStr">
@@ -3180,12 +3172,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3203,7 +3195,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3215,318 +3207,318 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Cybersecurity in the Age of AI</t>
+          <t>Microsoft AI Tour - Mumbai</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46434</v>
+        <v>46428</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Xchange 2027</t>
+          <t>Microsoft AI Tour - Bengaluru</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46453</v>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>46455</v>
-      </c>
+        <v>46433</v>
+      </c>
+      <c r="C59" s="2" t="n"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>The Channel Company</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>https://event.thechannelco.com/xchange-march/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Xchange (The Channel Co)</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - New York City</t>
+          <t>ChannelPro DEEP DIVE: Cybersecurity in the Age of AI</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46464</v>
+        <v>46434</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Perfecting Your Tool Stack</t>
+          <t>Xchange 2027</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46483</v>
-      </c>
-      <c r="C61" s="2" t="n"/>
+        <v>46453</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46455</v>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>The Channel Company</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
+          <t>https://event.thechannelco.com/xchange-march/</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
+          <t>Xchange (The Channel Co)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
+          <t>Microsoft AI Tour - New York City</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46539</v>
+        <v>46464</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour - Houston</t>
+          <t>ChannelPro DEEP DIVE: Perfecting Your Tool Stack</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46540</v>
+        <v>46483</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ChannelPro Network</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Microsoft AI Tour</t>
+          <t>Channel Pro Network</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Databricks Data+AI Summit 2027</t>
+          <t>Global Channel Growth Summit 2027</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46559</v>
+        <v>46490</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46562</v>
+        <v>46492</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Channel Marketing Association</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/dataaisummit/agenda</t>
+          <t>https://www.channelmarketingassociation.com/Global-Summit-2027</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Databricks Data+AI Summit</t>
+          <t>CMA Global Channel Growth Summit</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
+          <t>ChannelPro DEEP DIVE: The Most Profitable Cybersecurity Services in 2027</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46623</v>
+        <v>46539</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" t="inlineStr">
@@ -3551,7 +3543,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -3563,18 +3555,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2027 ChannelPro DEFEND: Dallas</t>
+          <t>Microsoft AI Tour - Houston</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46644</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>46645</v>
-      </c>
+        <v>46540</v>
+      </c>
+      <c r="C66" s="2" t="n"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ChannelPro Network</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3582,38 +3572,50 @@
           <t>Texas</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Channel Pro Network</t>
+          <t>Microsoft AI Tour</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dreamforce 2027</t>
+          <t>Databricks Data+AI Summit 2027</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46651</v>
+        <v>46559</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>46653</v>
+        <v>46562</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3625,7 +3627,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3637,23 +3639,23 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com/dreamforce/</t>
+          <t>https://www.databricks.com/dataaisummit/agenda</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Dreamforce</t>
+          <t>Databricks Data+AI Summit</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
+          <t>ChannelPro DEEP DIVE: Where the Next Wave of MSP Revenue Is Coming From</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46679</v>
+        <v>46623</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" t="inlineStr">
@@ -3678,10 +3680,141 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr">
         <is>
+          <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2027 ChannelPro DEFEND: Dallas</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>46644</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46645</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChannelPro Network</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Channel Pro Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dreamforce 2027</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>46651</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46653</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.salesforce.com/dreamforce/</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Dreamforce</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ChannelPro DEEP DIVE: The AI-Powered MSP</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>46679</v>
+      </c>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChannelPro Network</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Channel Pro Network</t>
         </is>
@@ -3724,7 +3857,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId39"/>
@@ -3739,10 +3872,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId54"/>
   </tableParts>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2027" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1635,8 +1635,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t>https://luma.com/agentsinnyc</t>
@@ -1751,7 +1749,6 @@
       <c r="C27" s="2" t="n">
         <v>46338</v>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -1772,9 +1769,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" s="3" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003698327636</t>
@@ -1821,13 +1815,11 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Seattle Data, AI &amp; Security</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/seattledataaiandsecurity/events/316481475/</t>
@@ -1899,7 +1891,6 @@
       <c r="C30" s="2" t="n">
         <v>46343</v>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -1920,9 +1911,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
@@ -1969,9 +1957,6 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t>https://www.joincatalyst.com/catalyst-breakfast-at-microsoft-ignite</t>
@@ -2095,16 +2080,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
           <t>https://www.channelmarketingassociation.com/industry-events</t>
@@ -2126,22 +2106,16 @@
         <v>46365</v>
       </c>
       <c r="C35" s="2" t="n"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr">
         <is>
           <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
@@ -2178,7 +2152,6 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2189,8 +2162,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
@@ -2346,7 +2317,6 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2357,8 +2327,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
@@ -2395,7 +2363,6 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2406,8 +2373,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
@@ -2439,16 +2404,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
@@ -2482,12 +2442,6 @@
           <t>Texas</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>https://event.thechannelco.com/xchange-march/</t>
@@ -2524,7 +2478,6 @@
           <t>New York City</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2535,8 +2488,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
@@ -2568,16 +2519,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
@@ -2611,12 +2557,6 @@
           <t>Texas</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>https://www.channelmarketingassociation.com/Global-Summit-2027</t>
@@ -2648,16 +2588,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
@@ -2694,7 +2629,6 @@
           <t>Houston</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2705,8 +2639,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
@@ -2740,8 +2672,6 @@
           <t>Bay Area</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Databricks</t>
@@ -2752,8 +2682,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>https://www.databricks.com/dataaisummit/agenda</t>
@@ -2785,16 +2713,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
@@ -2828,12 +2751,6 @@
           <t>Texas</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
@@ -2872,7 +2789,6 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Salesforce</t>
@@ -2883,8 +2799,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t>https://www.salesforce.com/dreamforce/</t>
@@ -2916,16 +2830,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2027" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,8 +147,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events2026" displayName="Events2026" ref="A1:M36" headerRowCount="1">
-  <autoFilter ref="A1:M36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Events2026" displayName="Events2026" ref="A1:M34" headerRowCount="1">
+  <autoFilter ref="A1:M34"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Date"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -615,16 +615,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Agents Seattle – August 2026</t>
+          <t>AI Agents in the Wild: Building, Scaling &amp; Deploying in Production</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AI / Claude ecosystem</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>AWS, Salesforce</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -661,16 +661,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Agents in the Wild: Building, Scaling &amp; Deploying in Production</t>
+          <t>NVIDIA Spark Hack: Seattle</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Salesforce / AWS</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AWS, Salesforce</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Not publicly listed</t>
+          <t>No public fee listed; approval required</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -707,16 +707,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVIDIA Spark Hack: Seattle</t>
+          <t>ISV Partner Event</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No public fee listed; approval required</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -753,16 +753,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ISV Partner Event</t>
+          <t>MICROSOFT 365, DATA &amp; POWER PLATFORM CONFERENCES</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="C6" s="2" t="n"/>
+        <v>46258</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46262</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -782,12 +784,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>1595-2695</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.techcon365.com/Seattle/</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -799,7 +806,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MICROSOFT 365, DATA &amp; POWER PLATFORM CONFERENCES</t>
+          <t>TechCon 365, DATACON &amp; PWRCON Seattle 2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -835,12 +842,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1595-2695</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.techcon365.com/Seattle/</t>
+          <t>$1,825–$2,995 currently, depending on pass</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -852,18 +854,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TechCon 365, DATACON &amp; PWRCON Seattle 2026</t>
+          <t>AWS Marketplace Seller Forum</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46258</v>
+        <v>46266</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -873,7 +875,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -883,12 +885,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>$1,825–$2,995 currently, depending on pass</t>
+          <t>Invite only event</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/marketplace/resources/events/seller-conference</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -900,18 +907,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Marketplace Seller Forum</t>
+          <t>AI, Zero Trust &amp; Enterprise Resilience in the Age of Continuous Disruption</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>46267</v>
-      </c>
+        <v>46275</v>
+      </c>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -931,17 +936,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Oracle, Intuit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Invite only event</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>https://aws.amazon.com/marketplace/resources/events/seller-conference</t>
+          <t>Not publicly listed</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI, Zero Trust &amp; Enterprise Resilience in the Age of Continuous Disruption</t>
+          <t>CISOMeet Seattle</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -962,7 +962,7 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Intuit / Oracle</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Oracle, Intuit</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Not publicly listed</t>
+          <t>No public fee listed; CISO/Sr. InfoSec qualification</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CISOMeet Seattle</t>
+          <t>World Forum</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1008,17 +1008,17 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>No public fee listed; CISO/Sr. InfoSec qualification</t>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.servicenow.com/events/world-forum.html</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1045,26 +1045,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>World Forum</t>
+          <t>Dreamforce 2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C12" s="2" t="n"/>
+        <v>46280</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>46282</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1074,12 +1076,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>https://www.servicenow.com/events/world-forum.html</t>
+          <t>https://www.salesforce.com/dreamforce/?d=pb</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1091,28 +1093,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dreamforce 2026</t>
+          <t>Amazon Accelerate 2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1122,12 +1124,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.salesforce.com/dreamforce/?d=pb</t>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Price not publicly surfaced; $100 early-bird discount through Aug 8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1139,18 +1141,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amazon Accelerate 2026</t>
+          <t>Build with Gemini – Seattle</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>46289</v>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Amazon / AWS ecosystem</t>
+          <t>Google Cloud</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Price not publicly surfaced; $100 early-bird discount through Aug 8</t>
+          <t>Free / complimentary</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1187,18 +1187,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IA40 Summit 2026</t>
+          <t>Official Cybersecurity Summit – Seattle/Bellevue</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46294</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>46295</v>
-      </c>
+        <v>46296</v>
+      </c>
+      <c r="C15" s="2" t="n"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AI ecosystem / Microsoft / AWS / Databricks</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1208,7 +1206,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1218,12 +1216,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Microsoft, AWS, Databricks</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Invite-only / no public fee</t>
+          <t>$250 standard admission</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1235,26 +1233,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Build with Gemini – Seattle</t>
+          <t>Cypher 2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46295</v>
-      </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Google Cloud</t>
-        </is>
+        <v>46301</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>46303</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1262,14 +1257,14 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Free / complimentary</t>
+          <t>7000 (INR)</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>https://kripeshadwani.com/best-tech-events-in-india/#ai-impact-summit-2026</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1281,26 +1276,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Official Cybersecurity Summit – Seattle/Bellevue</t>
+          <t>World Forum</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IBM / Cybersecurity ecosystem</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1310,12 +1305,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>$250 standard admission</t>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.servicenow.com/events/world-forum.html</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1327,23 +1322,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cypher 2026</t>
+          <t>TechCrunch Disrupt 2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1353,12 +1348,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7000 (INR)</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>https://kripeshadwani.com/best-tech-events-in-india/#ai-impact-summit-2026</t>
+          <t>https://techcrunch.com/events/tc-disrupt-2026/</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1370,26 +1365,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>World Forum</t>
+          <t>ElevateIT Seattle Technology Summit 2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46301</v>
+        <v>46309</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1399,12 +1394,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.servicenow.com/events/world-forum.html</t>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not publicly listed</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1416,14 +1411,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TechCrunch Disrupt 2026</t>
+          <t>Cloudflare Connect</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46310</v>
+        <v>46317</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1440,14 +1440,14 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/events/tc-disrupt-2026/</t>
+          <t>https://www.cloudflare.com/en-gb/lp/cloudflare-connect-2026/</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1459,16 +1459,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ElevateIT Seattle Technology Summit 2026</t>
+          <t>Seattle AI Week 2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C21" s="2" t="n"/>
+        <v>46321</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46325</v>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nutanix / Enterprise IT ecosystem</t>
+          <t>Multi-vendor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1486,14 +1488,9 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Not publicly listed</t>
+          <t>Varies by event; flagship Summit EB $175</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1505,28 +1502,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloudflare Connect</t>
+          <t>Agents in NYC</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46314</v>
+        <v>46323</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46317</v>
+        <v>46323</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Datadog, Albert Zhao, Datadog</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1536,35 +1533,42 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>https://www.cloudflare.com/en-gb/lp/cloudflare-connect-2026/</t>
+          <t>https://luma.com/agentsinnyc</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Luma NYC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Seattle AI Week 2026</t>
+          <t>SecureWorld Seattle 2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46321</v>
+        <v>46330</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46325</v>
+        <v>46331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Multi-vendor / AI ecosystem</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1574,7 +1578,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1582,9 +1586,14 @@
           <t>In-person</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Google, Cohesity, Blue Yonder, OpenAI</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Varies by event; flagship Summit EB $175</t>
+          <t>Multiple pass types; current price not publicly surfaced in indexed page</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1596,28 +1605,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Agents in NYC</t>
+          <t>PASS Data Community Summit West</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46323</v>
+        <v>46335</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46323</v>
+        <v>46337</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Datadog, Albert Zhao, Datadog</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1625,44 +1634,30 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>https://luma.com/agentsinnyc</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>$1,790–$1,990 for published 2-day ticket</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Luma NYC</t>
+          <t>Legacy tracker 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SecureWorld Seattle 2026</t>
+          <t>SaaSify Partner Central Agentic Workshop</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46330</v>
+        <v>46338</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46331</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>OpenAI / Google Cloud / Cohesity / Blue Yonder</t>
-        </is>
-      </c>
+        <v>46338</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -1670,7 +1665,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1680,35 +1675,36 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Google, Cohesity, Blue Yonder, OpenAI</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Multiple pass types; current price not publicly surfaced in indexed page</t>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003698327636</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Eventbrite Seattle - AWS/Microsoft/Google</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PASS Data Community Summit West</t>
+          <t>Identity, AI &amp; Cybersecurity: Securing the Enterprise in an Agentic World</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46335</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>46337</v>
-      </c>
+        <v>46339</v>
+      </c>
+      <c r="C26" s="2" t="n"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Data / Cloud ecosystem</t>
+          <t>Seattle Data, AI &amp; Security</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1718,7 +1714,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1726,37 +1722,54 @@
           <t>In-person</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>$1,790–$1,990 for published 2-day ticket</t>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Seattle Data, AI &amp; Security</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/seattledataaiandsecurity/events/316481475/</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Meetup Seattle - AWS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SaaSify Partner Central Agentic Workshop</t>
+          <t>Microsoft Ignite 2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46338</v>
+        <v>46343</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46338</v>
+        <v>46346</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1766,43 +1779,41 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003698327636</t>
+          <t>https://ignite.microsoft.com/en-US/home</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Eventbrite Seattle - AWS/Microsoft/Google</t>
+          <t>Legacy tracker 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Identity, AI &amp; Cybersecurity: Securing the Enterprise in an Agentic World</t>
+          <t>SaaSify Partner Central Agentic Workshop</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46339</v>
-      </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Seattle Data, AI &amp; Security</t>
-        </is>
-      </c>
+        <v>46343</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46343</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1812,84 +1823,86 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Seattle Data, AI &amp; Security</t>
-        </is>
-      </c>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/seattledataaiandsecurity/events/316481475/</t>
+          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Meetup Seattle - AWS</t>
+          <t>Eventbrite SF - cloud partner</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Microsoft Ignite 2026</t>
+          <t>Catalyst Breakfast at Microsoft Ignite</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>46346</v>
-      </c>
+        <v>46344</v>
+      </c>
+      <c r="C29" s="2" t="n"/>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Partnership Leaders</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>https://ignite.microsoft.com/en-US/home</t>
+          <t>https://www.joincatalyst.com/catalyst-breakfast-at-microsoft-ignite</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Partnership Leaders events</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SaaSify Partner Central Agentic Workshop</t>
+          <t>Cloudflare Immerse</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>46343</v>
+        <v>46346</v>
+      </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1898,7 +1911,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1908,43 +1921,43 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
+          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Eventbrite SF - cloud partner</t>
+          <t>Legacy tracker 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Catalyst Breakfast at Microsoft Ignite</t>
+          <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46344</v>
+        <v>46357</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Partnership Leaders</t>
+          <t>Google Cloud</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1954,220 +1967,142 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>https://www.joincatalyst.com/catalyst-breakfast-at-microsoft-ignite</t>
+          <t>Google, Dynatrace, Cloudflare</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Invite/application-based; no public attendee fee</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Partnership Leaders events</t>
+          <t>Legacy tracker 2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloudflare Immerse</t>
+          <t>CMA Power Circles</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46346</v>
+        <v>46358</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Channel Marketing Association</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Bay Area</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>https://fieldmarketing.www.cloudflare.com/cloudflareimmersebayarea?_gl=1*1ge1j1x*_gcl_au*MjMxOTM0MjE4LjE3NTkzNjYwMjI.*_ga*ZmI3OTU3NjUtZDkyOC00M2I3LWJiOGYtNzQ5ZjJlZGUxYWFm*_ga_SQCRB0TXZW*czE3NjU0NjEwMDIkbzMkZzEkdDE3NjU0NjEwNTkkajMkbDAkaDAkZHVGb1hkWDJpQmU2OUExYjJSSl92c2xTbkxWQURDZTlUSWc.</t>
+          <t>https://www.channelmarketingassociation.com/industry-events</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>Channel Marketing Association events</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gartner / Evanta Seattle CIO Community Executive Summit</t>
+          <t>MSP Summit: AI Symposium</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46357</v>
+        <v>46365</v>
       </c>
       <c r="C33" s="2" t="n"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Google Cloud / Cloudflare / Dynatrace</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Google, Dynatrace, Cloudflare</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Invite/application-based; no public attendee fee</t>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Legacy tracker 2026</t>
+          <t>MSP Summit / events calendar</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CMA Power Circles</t>
+          <t>Microsoft AI Tour - Seattle</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46358</v>
+        <v>46365</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Channel Marketing Association</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://www.channelmarketingassociation.com/industry-events</t>
+          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
-        <is>
-          <t>Channel Marketing Association events</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>MSP Summit: AI Symposium</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>46365</v>
-      </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>MSP Summit / events calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Microsoft AI Tour - Seattle</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>46365</v>
-      </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
         <is>
           <t>Microsoft AI Tour</t>
         </is>
@@ -2175,24 +2110,24 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2317,6 +2252,7 @@
           <t>Mumbai</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2327,6 +2263,8 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
@@ -2363,6 +2301,7 @@
           <t>Bengaluru</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2373,6 +2312,8 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
@@ -2404,11 +2345,16 @@
           <t>Virtual</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
@@ -2442,6 +2388,12 @@
           <t>Texas</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>https://event.thechannelco.com/xchange-march/</t>
@@ -2478,6 +2430,7 @@
           <t>New York City</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2488,6 +2441,8 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
@@ -2519,11 +2474,16 @@
           <t>Virtual</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
@@ -2557,6 +2517,12 @@
           <t>Texas</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>https://www.channelmarketingassociation.com/Global-Summit-2027</t>
@@ -2588,11 +2554,16 @@
           <t>Virtual</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
@@ -2629,6 +2600,7 @@
           <t>Houston</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2639,6 +2611,8 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
@@ -2672,6 +2646,8 @@
           <t>Bay Area</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Databricks</t>
@@ -2682,6 +2658,8 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>https://www.databricks.com/dataaisummit/agenda</t>
@@ -2713,11 +2691,16 @@
           <t>Virtual</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
@@ -2751,6 +2734,12 @@
           <t>Texas</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
@@ -2789,6 +2778,7 @@
           <t>San Francisco</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Salesforce</t>
@@ -2799,6 +2789,8 @@
           <t>Host</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t>https://www.salesforce.com/dreamforce/</t>
@@ -2830,11 +2822,16 @@
           <t>Virtual</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1541,8 +1541,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr">
         <is>
           <t>https://luma.com/agentsinnyc</t>
@@ -1657,7 +1655,6 @@
       <c r="C25" s="2" t="n">
         <v>46338</v>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -1678,9 +1675,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003698327636</t>
@@ -1727,13 +1721,11 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Seattle Data, AI &amp; Security</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" s="3" t="inlineStr">
         <is>
           <t>https://www.meetup.com/seattledataaiandsecurity/events/316481475/</t>
@@ -1805,7 +1797,6 @@
       <c r="C28" s="2" t="n">
         <v>46343</v>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Bay Area</t>
@@ -1826,9 +1817,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/saasify-partner-central-agentic-workshop-tickets-2003695905391</t>
@@ -1875,9 +1863,6 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
           <t>https://www.joincatalyst.com/catalyst-breakfast-at-microsoft-ignite</t>
@@ -2001,16 +1986,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
           <t>https://www.channelmarketingassociation.com/industry-events</t>
@@ -2032,22 +2012,16 @@
         <v>46365</v>
       </c>
       <c r="C33" s="2" t="n"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" s="3" t="inlineStr">
         <is>
           <t>https://themspsummit.com/msp-summit-ai-symposium/</t>
@@ -2084,7 +2058,6 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2095,8 +2068,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/seattle27/citylanding/page/cityhome</t>
@@ -2252,7 +2223,6 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2263,8 +2233,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymemumbai/page/notifyme</t>
@@ -2301,7 +2269,6 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2312,8 +2279,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymebengaluru/page/notifyme</t>
@@ -2345,16 +2310,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-cybersecurity-in-the-age-of-ai/</t>
@@ -2388,12 +2348,6 @@
           <t>Texas</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>https://event.thechannelco.com/xchange-march/</t>
@@ -2430,7 +2384,6 @@
           <t>New York City</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2441,8 +2394,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymenyc/page/notifyme</t>
@@ -2474,16 +2425,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-perfecting-your-tool-stack/</t>
@@ -2517,12 +2463,6 @@
           <t>Texas</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>https://www.channelmarketingassociation.com/Global-Summit-2027</t>
@@ -2554,16 +2494,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-most-profitable-cybersecurity-services-in-2027/</t>
@@ -2600,7 +2535,6 @@
           <t>Houston</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -2611,8 +2545,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>https://aitour.microsoft.com/flow/microsoft/tour/notifymehouston/page/notifyme</t>
@@ -2646,8 +2578,6 @@
           <t>Bay Area</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Databricks</t>
@@ -2658,8 +2588,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>https://www.databricks.com/dataaisummit/agenda</t>
@@ -2691,16 +2619,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-where-the-next-wave-of-msp-revenue-is-coming-from/</t>
@@ -2734,12 +2657,6 @@
           <t>Texas</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/2027-channelpro-defend-dallas/</t>
@@ -2778,7 +2695,6 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Salesforce</t>
@@ -2789,8 +2705,6 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t>https://www.salesforce.com/dreamforce/</t>
@@ -2822,16 +2736,11 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>https://events.channelpronetwork.com/channelpro-deep-dive-the-ai-powered-msp/</t>
